--- a/docs/enterprise_data_warehouse_bus_matrix.xlsx
+++ b/docs/enterprise_data_warehouse_bus_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Documents\GitHub\dwh-adventureworks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A302E6-5F05-4EF1-AEEE-E9E580B14F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550C8BF0-5248-433C-958B-133AACE69AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definitions" sheetId="2" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="490">
   <si>
     <t>Story Point Values</t>
   </si>
@@ -1516,6 +1516,42 @@
   </si>
   <si>
     <t>dim_store</t>
+  </si>
+  <si>
+    <t>store_key</t>
+  </si>
+  <si>
+    <t>store_name</t>
+  </si>
+  <si>
+    <t>square_feet</t>
+  </si>
+  <si>
+    <t>year_opened</t>
+  </si>
+  <si>
+    <t>number_employee</t>
+  </si>
+  <si>
+    <t>specialty</t>
+  </si>
+  <si>
+    <t>brands</t>
+  </si>
+  <si>
+    <t>Informationg about the store such as the square feet of store.</t>
+  </si>
+  <si>
+    <t>Informationg about the store such as number of employees.</t>
+  </si>
+  <si>
+    <t>Informationg about the store such as year oppend.</t>
+  </si>
+  <si>
+    <t>Informationg about the store such as speciality.</t>
+  </si>
+  <si>
+    <t>Number of brands available.</t>
   </si>
 </sst>
 </file>
@@ -2373,6 +2409,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2415,18 +2457,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
     <dxf>
       <font>
         <b/>
@@ -2435,6 +2471,13 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2716,12 +2759,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DimTypesTbl" displayName="DimTypesTbl" ref="A40:C50" totalsRowShown="0" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DimTypesTbl" displayName="DimTypesTbl" ref="A40:C50" totalsRowShown="0" dataDxfId="24">
   <autoFilter ref="A40:C50" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dimension Types" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Definition" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ref" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dimension Types" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Definition" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ref" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2732,7 +2775,7 @@
   <autoFilter ref="A84:C87" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Hub Types"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Definitions" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Definitions" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Ref" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2752,8 +2795,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J107" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J107" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J119" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J119" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2782,12 +2825,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="FactTypesTbl" displayName="FactTypesTbl" ref="A30:C37" totalsRowShown="0" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="FactTypesTbl" displayName="FactTypesTbl" ref="A30:C37" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A30:C37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fact Types" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Definition" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Ref" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fact Types" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Definition" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Ref" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2838,7 +2881,7 @@
   <autoFilter ref="A53:C76" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Terms Dictionary"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Definition" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Definition" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Ref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4412,10 +4455,10 @@
       <c r="I8" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="109" t="s">
+      <c r="J8" s="95" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="108" t="s">
+      <c r="K8" s="94" t="s">
         <v>237</v>
       </c>
       <c r="L8" s="89" t="s">
@@ -4682,13 +4725,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D12:D1048576 D3:D5 D7:D10">
-    <cfRule type="duplicateValues" dxfId="13" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:XFD5 B5:E5">
-    <cfRule type="duplicateValues" dxfId="12" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="11" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
     <cfRule type="colorScale" priority="121">
@@ -4727,10 +4770,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5">
-    <cfRule type="duplicateValues" dxfId="10" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5">
-    <cfRule type="duplicateValues" dxfId="9" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
     <cfRule type="colorScale" priority="72">
@@ -4745,13 +4788,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE5 J5 O5">
-    <cfRule type="duplicateValues" dxfId="8" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI5 X5">
-    <cfRule type="duplicateValues" dxfId="7" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="duplicateValues" dxfId="6" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
     <cfRule type="colorScale" priority="853">
@@ -4766,7 +4809,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="5" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
     <cfRule type="colorScale" priority="67">
@@ -4781,7 +4824,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5 M5">
-    <cfRule type="duplicateValues" dxfId="4" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2">
     <cfRule type="colorScale" priority="1082">
@@ -4808,7 +4851,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="3" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:AJ2">
     <cfRule type="colorScale" priority="1426">
@@ -4835,7 +4878,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK5 N5 R5:W5 Y5:AD5 AF5:AH5 L5">
-    <cfRule type="duplicateValues" dxfId="2" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1430"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E9:E10 J6:AJ6" xr:uid="{00000000-0002-0000-0000-000002000000}">
@@ -4867,7 +4910,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -8029,18 +8072,308 @@
       <c r="C107" t="s">
         <v>477</v>
       </c>
+      <c r="D107" t="s">
+        <v>478</v>
+      </c>
+      <c r="E107" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" t="s">
+        <v>477</v>
+      </c>
+      <c r="D108" t="s">
+        <v>479</v>
+      </c>
+      <c r="E108" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" t="s">
+        <v>477</v>
+      </c>
+      <c r="D109" t="s">
+        <v>480</v>
+      </c>
+      <c r="E109" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>235</v>
+      </c>
+      <c r="B110" t="s">
+        <v>80</v>
+      </c>
+      <c r="C110" t="s">
+        <v>477</v>
+      </c>
+      <c r="D110" t="s">
+        <v>481</v>
+      </c>
+      <c r="E110" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>235</v>
+      </c>
+      <c r="B111" t="s">
+        <v>80</v>
+      </c>
+      <c r="C111" t="s">
+        <v>477</v>
+      </c>
+      <c r="D111" t="s">
+        <v>482</v>
+      </c>
+      <c r="E111" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>235</v>
+      </c>
+      <c r="B112" t="s">
+        <v>80</v>
+      </c>
+      <c r="C112" t="s">
+        <v>477</v>
+      </c>
+      <c r="D112" t="s">
+        <v>483</v>
+      </c>
+      <c r="E112" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" t="s">
+        <v>477</v>
+      </c>
+      <c r="D113" t="s">
+        <v>484</v>
+      </c>
+      <c r="E113" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>235</v>
+      </c>
+      <c r="B114" t="s">
+        <v>80</v>
+      </c>
+      <c r="C114" t="s">
+        <v>477</v>
+      </c>
+      <c r="D114" t="s">
+        <v>328</v>
+      </c>
+      <c r="E114" t="s">
+        <v>329</v>
+      </c>
+      <c r="F114" t="s">
+        <v>439</v>
+      </c>
+      <c r="G114" t="s">
+        <v>439</v>
+      </c>
+      <c r="H114" t="s">
+        <v>439</v>
+      </c>
+      <c r="I114" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>235</v>
+      </c>
+      <c r="B115" t="s">
+        <v>80</v>
+      </c>
+      <c r="C115" t="s">
+        <v>477</v>
+      </c>
+      <c r="D115" t="s">
+        <v>330</v>
+      </c>
+      <c r="E115" t="s">
+        <v>331</v>
+      </c>
+      <c r="F115" t="s">
+        <v>439</v>
+      </c>
+      <c r="G115" t="s">
+        <v>439</v>
+      </c>
+      <c r="H115" t="s">
+        <v>439</v>
+      </c>
+      <c r="I115" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>235</v>
+      </c>
+      <c r="B116" t="s">
+        <v>80</v>
+      </c>
+      <c r="C116" t="s">
+        <v>477</v>
+      </c>
+      <c r="D116" t="s">
+        <v>332</v>
+      </c>
+      <c r="E116" t="s">
+        <v>333</v>
+      </c>
+      <c r="F116" t="s">
+        <v>439</v>
+      </c>
+      <c r="G116" t="s">
+        <v>439</v>
+      </c>
+      <c r="H116" t="s">
+        <v>439</v>
+      </c>
+      <c r="I116" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>235</v>
+      </c>
+      <c r="B117" t="s">
+        <v>80</v>
+      </c>
+      <c r="C117" t="s">
+        <v>477</v>
+      </c>
+      <c r="D117" t="s">
+        <v>334</v>
+      </c>
+      <c r="E117" t="s">
+        <v>335</v>
+      </c>
+      <c r="F117" t="s">
+        <v>439</v>
+      </c>
+      <c r="G117" t="s">
+        <v>439</v>
+      </c>
+      <c r="H117" t="s">
+        <v>439</v>
+      </c>
+      <c r="I117" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>235</v>
+      </c>
+      <c r="B118" t="s">
+        <v>80</v>
+      </c>
+      <c r="C118" t="s">
+        <v>477</v>
+      </c>
+      <c r="D118" t="s">
+        <v>336</v>
+      </c>
+      <c r="E118" t="s">
+        <v>337</v>
+      </c>
+      <c r="F118" t="s">
+        <v>439</v>
+      </c>
+      <c r="G118" t="s">
+        <v>439</v>
+      </c>
+      <c r="H118" t="s">
+        <v>439</v>
+      </c>
+      <c r="I118" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" t="s">
+        <v>80</v>
+      </c>
+      <c r="C119" t="s">
+        <v>477</v>
+      </c>
+      <c r="D119" t="s">
+        <v>338</v>
+      </c>
+      <c r="E119" t="s">
+        <v>339</v>
+      </c>
+      <c r="F119" t="s">
+        <v>439</v>
+      </c>
+      <c r="G119" t="s">
+        <v>439</v>
+      </c>
+      <c r="H119" t="s">
+        <v>439</v>
+      </c>
+      <c r="I119" t="s">
+        <v>439</v>
+      </c>
+      <c r="J119" t="s">
+        <v>424</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F109:F112">
-    <cfRule type="expression" dxfId="1" priority="1432">
+  <conditionalFormatting sqref="F113:F115">
+    <cfRule type="expression" dxfId="2" priority="1432">
+      <formula>AND($A112&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F112">
+    <cfRule type="expression" dxfId="1" priority="1433">
       <formula>AND($A108&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A107" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A119" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>SchemaList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B107" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B119" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>ObjectTypeList</formula1>
     </dataValidation>
   </dataValidations>
@@ -8088,54 +8421,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="98" t="s">
+      <c r="C1" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="99"/>
-      <c r="E1" s="98" t="s">
+      <c r="D1" s="101"/>
+      <c r="E1" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="102" t="s">
+      <c r="F1" s="102"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="103"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="102" t="s">
+      <c r="I1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="104"/>
-      <c r="M1" s="102" t="s">
+      <c r="L1" s="106"/>
+      <c r="M1" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="96"/>
+      <c r="N1" s="98"/>
       <c r="O1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="102" t="s">
+      <c r="P1" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="98" t="s">
+      <c r="Q1" s="106"/>
+      <c r="R1" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="96" t="s">
+      <c r="S1" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="96" t="s">
+      <c r="T1" s="98" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95"/>
-      <c r="B2" s="106"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="108"/>
       <c r="C2" s="11" t="s">
         <v>29</v>
       </c>
@@ -8181,9 +8514,9 @@
       <c r="Q2" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="107"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>

--- a/docs/enterprise_data_warehouse_bus_matrix.xlsx
+++ b/docs/enterprise_data_warehouse_bus_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Documents\GitHub\dwh-adventureworks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550C8BF0-5248-433C-958B-133AACE69AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C926F373-92B6-4741-B250-D45060625CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="491">
   <si>
     <t>Story Point Values</t>
   </si>
@@ -1553,12 +1553,15 @@
   <si>
     <t>Number of brands available.</t>
   </si>
+  <si>
+    <t>Demographics</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1625,6 +1628,14 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1659,13 +1670,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2404,15 +2415,14 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2457,6 +2467,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2466,11 +2477,21 @@
     <dxf>
       <font>
         <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4455,10 +4476,10 @@
       <c r="I8" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="95" t="s">
+      <c r="J8" s="94" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="94" t="s">
+      <c r="K8" s="93" t="s">
         <v>237</v>
       </c>
       <c r="L8" s="89" t="s">
@@ -4926,34 +4947,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="91" t="s">
+      <c r="D1" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="91" t="s">
+      <c r="H1" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="91" t="s">
+      <c r="I1" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="91" t="s">
+      <c r="J1" s="109" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8078,6 +8099,18 @@
       <c r="E107" t="s">
         <v>289</v>
       </c>
+      <c r="F107" t="s">
+        <v>439</v>
+      </c>
+      <c r="G107" t="s">
+        <v>439</v>
+      </c>
+      <c r="H107" t="s">
+        <v>439</v>
+      </c>
+      <c r="I107" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
@@ -8095,6 +8128,18 @@
       <c r="E108" t="s">
         <v>429</v>
       </c>
+      <c r="F108" t="s">
+        <v>393</v>
+      </c>
+      <c r="G108" t="s">
+        <v>394</v>
+      </c>
+      <c r="H108" t="s">
+        <v>402</v>
+      </c>
+      <c r="I108" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -8112,6 +8157,18 @@
       <c r="E109" t="s">
         <v>485</v>
       </c>
+      <c r="F109" t="s">
+        <v>393</v>
+      </c>
+      <c r="G109" t="s">
+        <v>394</v>
+      </c>
+      <c r="H109" t="s">
+        <v>402</v>
+      </c>
+      <c r="I109" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -8129,6 +8186,18 @@
       <c r="E110" t="s">
         <v>487</v>
       </c>
+      <c r="F110" t="s">
+        <v>393</v>
+      </c>
+      <c r="G110" t="s">
+        <v>394</v>
+      </c>
+      <c r="H110" t="s">
+        <v>402</v>
+      </c>
+      <c r="I110" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
@@ -8146,6 +8215,18 @@
       <c r="E111" t="s">
         <v>486</v>
       </c>
+      <c r="F111" t="s">
+        <v>393</v>
+      </c>
+      <c r="G111" t="s">
+        <v>394</v>
+      </c>
+      <c r="H111" t="s">
+        <v>402</v>
+      </c>
+      <c r="I111" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
@@ -8163,6 +8244,18 @@
       <c r="E112" t="s">
         <v>488</v>
       </c>
+      <c r="F112" t="s">
+        <v>393</v>
+      </c>
+      <c r="G112" t="s">
+        <v>394</v>
+      </c>
+      <c r="H112" t="s">
+        <v>402</v>
+      </c>
+      <c r="I112" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
@@ -8180,6 +8273,18 @@
       <c r="E113" t="s">
         <v>489</v>
       </c>
+      <c r="F113" t="s">
+        <v>393</v>
+      </c>
+      <c r="G113" t="s">
+        <v>394</v>
+      </c>
+      <c r="H113" t="s">
+        <v>402</v>
+      </c>
+      <c r="I113" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
@@ -8359,14 +8464,9 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F113:F115">
+  <conditionalFormatting sqref="F114:F115">
     <cfRule type="expression" dxfId="2" priority="1432">
-      <formula>AND($A112&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="1" priority="1433">
-      <formula>AND($A108&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
+      <formula>AND($A113&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -8421,54 +8521,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="100" t="s">
+      <c r="D1" s="100"/>
+      <c r="E1" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="104" t="s">
+      <c r="F1" s="101"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="105"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="104" t="s">
+      <c r="I1" s="104"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="104" t="s">
+      <c r="L1" s="105"/>
+      <c r="M1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="98"/>
+      <c r="N1" s="97"/>
       <c r="O1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="104" t="s">
+      <c r="P1" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="100" t="s">
+      <c r="Q1" s="105"/>
+      <c r="R1" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="98" t="s">
+      <c r="S1" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="98" t="s">
+      <c r="T1" s="97" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="108"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="107"/>
       <c r="C2" s="11" t="s">
         <v>29</v>
       </c>
@@ -8514,9 +8614,9 @@
       <c r="Q2" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="109"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
@@ -8621,15 +8721,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="91" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="91" t="s">
         <v>470</v>
       </c>
-      <c r="E2" s="93" t="str">
+      <c r="E2" s="92" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G2,FIND("]",G2)),"]",""),"[",""),"    ","")</f>
         <v>territory_key</v>
       </c>
@@ -8654,7 +8754,7 @@
       <c r="D3" s="83" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="93" t="str">
+      <c r="E3" s="92" t="str">
         <f t="shared" ref="E3:E6" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G3,FIND("]",G3)),"]",""),"[",""),"    ","")</f>
         <v>territory_name_bk</v>
       </c>
@@ -8679,7 +8779,7 @@
       <c r="D4" s="83" t="s">
         <v>433</v>
       </c>
-      <c r="E4" s="93" t="str">
+      <c r="E4" s="92" t="str">
         <f t="shared" si="0"/>
         <v>territory_group</v>
       </c>
@@ -8704,7 +8804,7 @@
       <c r="D5" s="83" t="s">
         <v>434</v>
       </c>
-      <c r="E5" s="93" t="str">
+      <c r="E5" s="92" t="str">
         <f t="shared" si="0"/>
         <v>country_region_code</v>
       </c>
@@ -8729,7 +8829,7 @@
       <c r="D6" s="83" t="s">
         <v>435</v>
       </c>
-      <c r="E6" s="93" t="str">
+      <c r="E6" s="92" t="str">
         <f t="shared" si="0"/>
         <v>country_name</v>
       </c>

--- a/docs/enterprise_data_warehouse_bus_matrix.xlsx
+++ b/docs/enterprise_data_warehouse_bus_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Documents\GitHub\dwh-adventureworks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C926F373-92B6-4741-B250-D45060625CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794E7F44-0641-4FE3-920A-BD61679924D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="498">
   <si>
     <t>Story Point Values</t>
   </si>
@@ -1555,6 +1555,27 @@
   </si>
   <si>
     <t>Demographics</t>
+  </si>
+  <si>
+    <t>dim_salesperson</t>
+  </si>
+  <si>
+    <t>salesperson_key</t>
+  </si>
+  <si>
+    <t>national_number_bk</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>job_title</t>
+  </si>
+  <si>
+    <t>hire_date</t>
+  </si>
+  <si>
+    <t>is_current_employee</t>
   </si>
 </sst>
 </file>
@@ -2425,6 +2446,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2467,13 +2489,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <b/>
@@ -2492,13 +2513,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2780,12 +2794,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DimTypesTbl" displayName="DimTypesTbl" ref="A40:C50" totalsRowShown="0" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DimTypesTbl" displayName="DimTypesTbl" ref="A40:C50" totalsRowShown="0" dataDxfId="23">
   <autoFilter ref="A40:C50" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dimension Types" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Definition" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ref" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dimension Types" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Definition" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ref" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2796,7 +2810,7 @@
   <autoFilter ref="A84:C87" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Hub Types"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Definitions" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Definitions" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Ref" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2816,8 +2830,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J119" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J119" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J131" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2846,12 +2860,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="FactTypesTbl" displayName="FactTypesTbl" ref="A30:C37" totalsRowShown="0" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="FactTypesTbl" displayName="FactTypesTbl" ref="A30:C37" totalsRowShown="0" dataDxfId="19">
   <autoFilter ref="A30:C37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fact Types" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Definition" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Ref" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Fact Types" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Definition" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Ref" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2902,7 +2916,7 @@
   <autoFilter ref="A53:C76" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Terms Dictionary"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Definition" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Definition" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Ref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4746,13 +4760,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D12:D1048576 D3:D5 D7:D10">
-    <cfRule type="duplicateValues" dxfId="14" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:XFD5 B5:E5">
-    <cfRule type="duplicateValues" dxfId="13" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="12" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
     <cfRule type="colorScale" priority="121">
@@ -4791,10 +4805,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5">
-    <cfRule type="duplicateValues" dxfId="11" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5">
-    <cfRule type="duplicateValues" dxfId="10" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
     <cfRule type="colorScale" priority="72">
@@ -4809,13 +4823,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE5 J5 O5">
-    <cfRule type="duplicateValues" dxfId="9" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI5 X5">
-    <cfRule type="duplicateValues" dxfId="8" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="duplicateValues" dxfId="7" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="852"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
     <cfRule type="colorScale" priority="853">
@@ -4830,7 +4844,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="6" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
     <cfRule type="colorScale" priority="67">
@@ -4845,7 +4859,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5 M5">
-    <cfRule type="duplicateValues" dxfId="5" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2">
     <cfRule type="colorScale" priority="1082">
@@ -4872,7 +4886,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="4" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:AJ2">
     <cfRule type="colorScale" priority="1426">
@@ -4899,7 +4913,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK5 N5 R5:W5 Y5:AD5 AF5:AH5 L5">
-    <cfRule type="duplicateValues" dxfId="3" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1430"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E9:E10 J6:AJ6" xr:uid="{00000000-0002-0000-0000-000002000000}">
@@ -4931,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -4947,34 +4961,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="109" t="s">
+      <c r="E1" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="109" t="s">
+      <c r="G1" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="109" t="s">
+      <c r="H1" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="109" t="s">
+      <c r="J1" s="95" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8463,17 +8477,224 @@
         <v>424</v>
       </c>
     </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>235</v>
+      </c>
+      <c r="B120" t="s">
+        <v>80</v>
+      </c>
+      <c r="C120" t="s">
+        <v>491</v>
+      </c>
+      <c r="D120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E120" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>235</v>
+      </c>
+      <c r="B121" t="s">
+        <v>80</v>
+      </c>
+      <c r="C121" t="s">
+        <v>491</v>
+      </c>
+      <c r="D121" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>235</v>
+      </c>
+      <c r="B122" t="s">
+        <v>80</v>
+      </c>
+      <c r="C122" t="s">
+        <v>491</v>
+      </c>
+      <c r="D122" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>235</v>
+      </c>
+      <c r="B123" t="s">
+        <v>80</v>
+      </c>
+      <c r="C123" t="s">
+        <v>491</v>
+      </c>
+      <c r="D123" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>235</v>
+      </c>
+      <c r="B124" t="s">
+        <v>80</v>
+      </c>
+      <c r="C124" t="s">
+        <v>491</v>
+      </c>
+      <c r="D124" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>235</v>
+      </c>
+      <c r="B125" t="s">
+        <v>80</v>
+      </c>
+      <c r="C125" t="s">
+        <v>491</v>
+      </c>
+      <c r="D125" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>235</v>
+      </c>
+      <c r="B126" t="s">
+        <v>80</v>
+      </c>
+      <c r="C126" t="s">
+        <v>491</v>
+      </c>
+      <c r="D126" t="s">
+        <v>328</v>
+      </c>
+      <c r="E126" t="s">
+        <v>329</v>
+      </c>
+      <c r="F126" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>235</v>
+      </c>
+      <c r="B127" t="s">
+        <v>80</v>
+      </c>
+      <c r="C127" t="s">
+        <v>491</v>
+      </c>
+      <c r="D127" t="s">
+        <v>330</v>
+      </c>
+      <c r="E127" t="s">
+        <v>331</v>
+      </c>
+      <c r="F127" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>235</v>
+      </c>
+      <c r="B128" t="s">
+        <v>80</v>
+      </c>
+      <c r="C128" t="s">
+        <v>491</v>
+      </c>
+      <c r="D128" t="s">
+        <v>332</v>
+      </c>
+      <c r="E128" t="s">
+        <v>333</v>
+      </c>
+      <c r="F128" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>235</v>
+      </c>
+      <c r="B129" t="s">
+        <v>80</v>
+      </c>
+      <c r="C129" t="s">
+        <v>491</v>
+      </c>
+      <c r="D129" t="s">
+        <v>334</v>
+      </c>
+      <c r="E129" t="s">
+        <v>335</v>
+      </c>
+      <c r="F129" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>235</v>
+      </c>
+      <c r="B130" t="s">
+        <v>80</v>
+      </c>
+      <c r="C130" t="s">
+        <v>491</v>
+      </c>
+      <c r="D130" t="s">
+        <v>336</v>
+      </c>
+      <c r="E130" t="s">
+        <v>337</v>
+      </c>
+      <c r="F130" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>235</v>
+      </c>
+      <c r="B131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131" t="s">
+        <v>491</v>
+      </c>
+      <c r="D131" t="s">
+        <v>338</v>
+      </c>
+      <c r="E131" t="s">
+        <v>339</v>
+      </c>
+      <c r="F131" t="s">
+        <v>439</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F114:F115">
-    <cfRule type="expression" dxfId="2" priority="1432">
+    <cfRule type="expression" dxfId="1" priority="1432">
       <formula>AND($A113&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A119" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A131" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>SchemaList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B119" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B131" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>ObjectTypeList</formula1>
     </dataValidation>
   </dataValidations>
@@ -8521,54 +8742,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="100"/>
-      <c r="E1" s="99" t="s">
+      <c r="D1" s="101"/>
+      <c r="E1" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103" t="s">
+      <c r="F1" s="102"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="104"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="103" t="s">
+      <c r="I1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="105"/>
-      <c r="M1" s="103" t="s">
+      <c r="L1" s="106"/>
+      <c r="M1" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="97"/>
+      <c r="N1" s="98"/>
       <c r="O1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="103" t="s">
+      <c r="P1" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="99" t="s">
+      <c r="Q1" s="106"/>
+      <c r="R1" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="97" t="s">
+      <c r="S1" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="97" t="s">
+      <c r="T1" s="98" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="96"/>
-      <c r="B2" s="107"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="108"/>
       <c r="C2" s="11" t="s">
         <v>29</v>
       </c>
@@ -8614,9 +8835,9 @@
       <c r="Q2" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="108"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>

--- a/docs/enterprise_data_warehouse_bus_matrix.xlsx
+++ b/docs/enterprise_data_warehouse_bus_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Documents\GitHub\dwh-adventureworks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794E7F44-0641-4FE3-920A-BD61679924D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1DB6C9-67D3-44A1-8CA6-ED2252BCC022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definitions" sheetId="2" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="533">
   <si>
     <t>Story Point Values</t>
   </si>
@@ -801,9 +801,6 @@
     <t>sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Each row </t>
-  </si>
-  <si>
     <t>dim_customer</t>
   </si>
   <si>
@@ -1512,9 +1509,6 @@
     <t>CountryRegion</t>
   </si>
   <si>
-    <t>dime_store</t>
-  </si>
-  <si>
     <t>dim_store</t>
   </si>
   <si>
@@ -1576,6 +1570,117 @@
   </si>
   <si>
     <t>is_current_employee</t>
+  </si>
+  <si>
+    <t>fact_sales</t>
+  </si>
+  <si>
+    <t>AdventureWorks2024</t>
+  </si>
+  <si>
+    <t>Each row per product sold.</t>
+  </si>
+  <si>
+    <t>Concatenate first name &amp; last name of source system.</t>
+  </si>
+  <si>
+    <t>sales_order_key</t>
+  </si>
+  <si>
+    <t>Primary key. One incremental unique number per product sold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV file, Pre Calculate </t>
+  </si>
+  <si>
+    <t>SalesOrderDetail</t>
+  </si>
+  <si>
+    <t>SalesOrderDetailID</t>
+  </si>
+  <si>
+    <t>sales_order_id_bk</t>
+  </si>
+  <si>
+    <t>SalesOrderID</t>
+  </si>
+  <si>
+    <t>Primary key. Foreign key to SalesOrderHeader.SalesOrderID.</t>
+  </si>
+  <si>
+    <t>OrderDate</t>
+  </si>
+  <si>
+    <t>OnlineOrderFlag</t>
+  </si>
+  <si>
+    <t>SalesPersonID</t>
+  </si>
+  <si>
+    <t>SalesOrderHeader</t>
+  </si>
+  <si>
+    <t>Dates the sales order was created.</t>
+  </si>
+  <si>
+    <t>0 = Order placed by sales person. 1 = Order placed online by customer.</t>
+  </si>
+  <si>
+    <t>Customer identification number. Foreign key to Customer.BusinessEntityID.</t>
+  </si>
+  <si>
+    <t>Sales person who created the sales order. Foreign key to SalesPerson.BusinessEntityID.</t>
+  </si>
+  <si>
+    <t>Territory in which the sale was made. Foreign key to SalesTerritory.SalesTerritoryID.</t>
+  </si>
+  <si>
+    <t>ProductID</t>
+  </si>
+  <si>
+    <t>online_order_flag</t>
+  </si>
+  <si>
+    <t>Product sold to customer. Foreign key to Product.ProductID.</t>
+  </si>
+  <si>
+    <t>OrderQty</t>
+  </si>
+  <si>
+    <t>UnitPrice</t>
+  </si>
+  <si>
+    <t>UnitPriceDiscount</t>
+  </si>
+  <si>
+    <t>LineTotal</t>
+  </si>
+  <si>
+    <t>Quantity ordered per product.</t>
+  </si>
+  <si>
+    <t>Selling price of a single product.</t>
+  </si>
+  <si>
+    <t>Discount amount.</t>
+  </si>
+  <si>
+    <t>Per product subtotal. Computed as UnitPrice * (1 - UnitPriceDiscount) * OrderQty.</t>
+  </si>
+  <si>
+    <t>order_quantity</t>
+  </si>
+  <si>
+    <t>unit_price</t>
+  </si>
+  <si>
+    <t>unit_price_discount</t>
+  </si>
+  <si>
+    <t>line_total</t>
+  </si>
+  <si>
+    <t>Bring with lookup</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1763,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1686,12 +1791,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2222,7 +2321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -2440,13 +2539,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2488,6 +2581,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2698,19 +2794,19 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>141886</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>37111</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>77932</xdr:rowOff>
+      <xdr:rowOff>173182</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>155863</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>125557</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>30307</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-      <mc:Choice Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="DWH Object Name">
@@ -2733,7 +2829,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2743,8 +2839,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="14533295" y="268432"/>
-              <a:ext cx="1226250" cy="2524125"/>
+              <a:off x="16134361" y="363682"/>
+              <a:ext cx="2067914" cy="2524125"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2830,8 +2926,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J131" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J131" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ObjectDefinition" displayName="ObjectDefinition" ref="A1:J149" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J149" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4106,7 +4202,7 @@
     <col min="6" max="6" width="5.5703125" style="33" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="46.5703125" style="33" customWidth="1"/>
     <col min="8" max="8" width="15.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="34.42578125" style="33" bestFit="1" customWidth="1"/>
     <col min="10" max="36" width="3.140625" style="31" customWidth="1"/>
     <col min="37" max="37" width="6.42578125" style="31" customWidth="1"/>
     <col min="38" max="38" width="28.42578125" style="31" customWidth="1"/>
@@ -4174,7 +4270,7 @@
       </c>
       <c r="O2" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="36">
         <f t="shared" si="0"/>
@@ -4275,18 +4371,20 @@
         <v>2</v>
       </c>
       <c r="K3" s="35">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="35">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M3" s="35">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N3" s="35">
-        <v>4</v>
-      </c>
-      <c r="O3" s="37"/>
+        <v>5</v>
+      </c>
+      <c r="O3" s="37">
+        <v>11</v>
+      </c>
       <c r="P3" s="37"/>
       <c r="Q3" s="37"/>
       <c r="R3" s="35"/>
@@ -4490,22 +4588,24 @@
       <c r="I8" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="108" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="K8" s="89" t="s">
         <v>237</v>
       </c>
       <c r="L8" s="89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M8" s="89" t="s">
-        <v>388</v>
-      </c>
-      <c r="N8" s="45" t="s">
-        <v>476</v>
-      </c>
-      <c r="O8" s="44"/>
+        <v>387</v>
+      </c>
+      <c r="N8" s="89" t="s">
+        <v>475</v>
+      </c>
+      <c r="O8" s="108" t="s">
+        <v>489</v>
+      </c>
       <c r="P8" s="44"/>
       <c r="Q8" s="44"/>
       <c r="R8" s="44"/>
@@ -4537,23 +4637,23 @@
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="48">
         <f>COUNTIF(F9:XR9,"~*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(J3:AJ3)</f>
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F9" s="49" t="s">
         <v>238</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H9" s="51" t="s">
         <v>50</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>239</v>
+        <v>498</v>
       </c>
       <c r="J9" s="53" t="s">
         <v>5</v>
@@ -4570,7 +4670,9 @@
       <c r="N9" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="53"/>
+      <c r="O9" s="53" t="s">
+        <v>5</v>
+      </c>
       <c r="P9" s="53"/>
       <c r="Q9" s="53"/>
       <c r="R9" s="54"/>
@@ -4646,20 +4748,22 @@
         <v>dim_date</v>
       </c>
       <c r="K11" s="67" t="str">
-        <f t="shared" ref="K11:L11" si="1">K8</f>
+        <f>K8</f>
         <v>dim_product</v>
       </c>
       <c r="L11" s="67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K11:L11" si="1">L8</f>
         <v>dim_customer</v>
       </c>
       <c r="M11" s="68" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N11" s="68" t="s">
-        <v>476</v>
-      </c>
-      <c r="O11" s="69"/>
+        <v>475</v>
+      </c>
+      <c r="O11" s="69" t="s">
+        <v>489</v>
+      </c>
       <c r="P11" s="67"/>
       <c r="Q11" s="67"/>
       <c r="R11" s="70"/>
@@ -4945,50 +5049,50 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="56.42578125" customWidth="1"/>
+    <col min="5" max="5" width="66.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="95" t="s">
+      <c r="E1" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="95" t="s">
+      <c r="F1" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="95" t="s">
+      <c r="H1" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="95" t="s">
+      <c r="I1" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="95" t="s">
+      <c r="J1" s="93" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5003,25 +5107,25 @@
         <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J2" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5035,25 +5139,25 @@
         <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J3" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5067,25 +5171,25 @@
         <v>236</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J4" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5099,25 +5203,25 @@
         <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J5" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -5131,25 +5235,25 @@
         <v>236</v>
       </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J6" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -5163,25 +5267,25 @@
         <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J7" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -5195,25 +5299,25 @@
         <v>236</v>
       </c>
       <c r="D8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J8" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -5227,25 +5331,25 @@
         <v>236</v>
       </c>
       <c r="D9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J9" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -5259,25 +5363,25 @@
         <v>236</v>
       </c>
       <c r="D10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J10" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -5291,25 +5395,25 @@
         <v>236</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J11" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -5323,25 +5427,25 @@
         <v>236</v>
       </c>
       <c r="D12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J12" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -5355,25 +5459,25 @@
         <v>236</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J13" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -5387,25 +5491,25 @@
         <v>236</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J14" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -5419,25 +5523,25 @@
         <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J15" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -5451,25 +5555,25 @@
         <v>236</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J16" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -5483,25 +5587,25 @@
         <v>236</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J17" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -5515,25 +5619,25 @@
         <v>236</v>
       </c>
       <c r="D18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J18" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5547,25 +5651,25 @@
         <v>236</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J19" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -5579,25 +5683,25 @@
         <v>236</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J20" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -5611,25 +5715,25 @@
         <v>236</v>
       </c>
       <c r="D21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J21" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -5643,25 +5747,25 @@
         <v>236</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J22" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5675,25 +5779,25 @@
         <v>236</v>
       </c>
       <c r="D23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J23" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5707,25 +5811,25 @@
         <v>236</v>
       </c>
       <c r="D24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J24" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -5739,25 +5843,25 @@
         <v>236</v>
       </c>
       <c r="D25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J25" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -5771,25 +5875,25 @@
         <v>236</v>
       </c>
       <c r="D26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J26" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -5803,25 +5907,25 @@
         <v>236</v>
       </c>
       <c r="D27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F27" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G27" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H27" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I27" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J27" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -5835,25 +5939,25 @@
         <v>236</v>
       </c>
       <c r="D28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F28" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G28" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H28" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I28" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J28" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5867,25 +5971,25 @@
         <v>236</v>
       </c>
       <c r="D29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F29" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G29" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H29" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I29" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J29" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -5899,25 +6003,25 @@
         <v>236</v>
       </c>
       <c r="D30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F30" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G30" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H30" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I30" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J30" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -5931,25 +6035,25 @@
         <v>236</v>
       </c>
       <c r="D31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J31" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -5963,25 +6067,25 @@
         <v>236</v>
       </c>
       <c r="D32" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F32" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G32" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H32" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I32" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J32" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5995,25 +6099,25 @@
         <v>236</v>
       </c>
       <c r="D33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J33" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -6027,25 +6131,25 @@
         <v>236</v>
       </c>
       <c r="D34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J34" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -6059,25 +6163,25 @@
         <v>236</v>
       </c>
       <c r="D35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J35" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6091,25 +6195,25 @@
         <v>236</v>
       </c>
       <c r="D36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J36" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -6123,25 +6227,25 @@
         <v>236</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E37" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J37" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -6155,25 +6259,25 @@
         <v>236</v>
       </c>
       <c r="D38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J38" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -6187,25 +6291,25 @@
         <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F39" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G39" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H39" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I39" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J39" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -6219,25 +6323,25 @@
         <v>236</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E40" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J40" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -6251,25 +6355,25 @@
         <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F41" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G41" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H41" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I41" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J41" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6283,25 +6387,25 @@
         <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J42" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -6315,25 +6419,25 @@
         <v>236</v>
       </c>
       <c r="D43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J43" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -6347,25 +6451,25 @@
         <v>236</v>
       </c>
       <c r="D44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E44" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J44" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -6379,25 +6483,25 @@
         <v>236</v>
       </c>
       <c r="D45" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E45" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J45" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -6411,25 +6515,25 @@
         <v>236</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E46" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F46" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G46" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H46" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I46" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J46" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -6443,25 +6547,25 @@
         <v>236</v>
       </c>
       <c r="D47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E47" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F47" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G47" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H47" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I47" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J47" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -6475,25 +6579,25 @@
         <v>236</v>
       </c>
       <c r="D48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E48" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J48" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -6507,25 +6611,25 @@
         <v>237</v>
       </c>
       <c r="D49" t="s">
+        <v>287</v>
+      </c>
+      <c r="E49" t="s">
         <v>288</v>
       </c>
-      <c r="E49" t="s">
-        <v>289</v>
-      </c>
       <c r="F49" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J49" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -6539,13 +6643,13 @@
         <v>237</v>
       </c>
       <c r="D50" t="s">
+        <v>289</v>
+      </c>
+      <c r="E50" t="s">
         <v>290</v>
       </c>
-      <c r="E50" t="s">
-        <v>291</v>
-      </c>
       <c r="F50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -6559,13 +6663,13 @@
         <v>237</v>
       </c>
       <c r="D51" t="s">
+        <v>291</v>
+      </c>
+      <c r="E51" t="s">
         <v>292</v>
       </c>
-      <c r="E51" t="s">
-        <v>293</v>
-      </c>
       <c r="F51" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -6579,13 +6683,13 @@
         <v>237</v>
       </c>
       <c r="D52" t="s">
+        <v>293</v>
+      </c>
+      <c r="E52" t="s">
         <v>294</v>
       </c>
-      <c r="E52" t="s">
-        <v>295</v>
-      </c>
       <c r="F52" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -6599,13 +6703,13 @@
         <v>237</v>
       </c>
       <c r="D53" t="s">
+        <v>295</v>
+      </c>
+      <c r="E53" t="s">
         <v>296</v>
       </c>
-      <c r="E53" t="s">
-        <v>297</v>
-      </c>
       <c r="F53" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -6619,13 +6723,13 @@
         <v>237</v>
       </c>
       <c r="D54" t="s">
+        <v>297</v>
+      </c>
+      <c r="E54" t="s">
         <v>298</v>
       </c>
-      <c r="E54" t="s">
-        <v>299</v>
-      </c>
       <c r="F54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -6639,13 +6743,13 @@
         <v>237</v>
       </c>
       <c r="D55" t="s">
+        <v>299</v>
+      </c>
+      <c r="E55" t="s">
         <v>300</v>
       </c>
-      <c r="E55" t="s">
-        <v>301</v>
-      </c>
       <c r="F55" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -6659,13 +6763,13 @@
         <v>237</v>
       </c>
       <c r="D56" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56" t="s">
         <v>302</v>
       </c>
-      <c r="E56" t="s">
-        <v>303</v>
-      </c>
       <c r="F56" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -6679,13 +6783,13 @@
         <v>237</v>
       </c>
       <c r="D57" t="s">
+        <v>303</v>
+      </c>
+      <c r="E57" t="s">
         <v>304</v>
       </c>
-      <c r="E57" t="s">
-        <v>305</v>
-      </c>
       <c r="F57" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -6699,13 +6803,13 @@
         <v>237</v>
       </c>
       <c r="D58" t="s">
+        <v>305</v>
+      </c>
+      <c r="E58" t="s">
         <v>306</v>
       </c>
-      <c r="E58" t="s">
-        <v>307</v>
-      </c>
       <c r="F58" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -6719,13 +6823,13 @@
         <v>237</v>
       </c>
       <c r="D59" t="s">
+        <v>307</v>
+      </c>
+      <c r="E59" t="s">
         <v>308</v>
       </c>
-      <c r="E59" t="s">
-        <v>309</v>
-      </c>
       <c r="F59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -6739,13 +6843,13 @@
         <v>237</v>
       </c>
       <c r="D60" t="s">
+        <v>309</v>
+      </c>
+      <c r="E60" t="s">
         <v>310</v>
       </c>
-      <c r="E60" t="s">
-        <v>311</v>
-      </c>
       <c r="F60" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6759,13 +6863,13 @@
         <v>237</v>
       </c>
       <c r="D61" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" t="s">
         <v>312</v>
       </c>
-      <c r="E61" t="s">
-        <v>313</v>
-      </c>
       <c r="F61" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -6779,13 +6883,13 @@
         <v>237</v>
       </c>
       <c r="D62" t="s">
+        <v>313</v>
+      </c>
+      <c r="E62" t="s">
         <v>314</v>
       </c>
-      <c r="E62" t="s">
-        <v>315</v>
-      </c>
       <c r="F62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -6799,13 +6903,13 @@
         <v>237</v>
       </c>
       <c r="D63" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" t="s">
         <v>316</v>
       </c>
-      <c r="E63" t="s">
-        <v>317</v>
-      </c>
       <c r="F63" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -6819,13 +6923,13 @@
         <v>237</v>
       </c>
       <c r="D64" t="s">
+        <v>317</v>
+      </c>
+      <c r="E64" t="s">
         <v>318</v>
       </c>
-      <c r="E64" t="s">
-        <v>319</v>
-      </c>
       <c r="F64" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -6839,13 +6943,13 @@
         <v>237</v>
       </c>
       <c r="D65" t="s">
+        <v>319</v>
+      </c>
+      <c r="E65" t="s">
         <v>320</v>
       </c>
-      <c r="E65" t="s">
-        <v>321</v>
-      </c>
       <c r="F65" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -6859,13 +6963,13 @@
         <v>237</v>
       </c>
       <c r="D66" t="s">
+        <v>321</v>
+      </c>
+      <c r="E66" t="s">
         <v>322</v>
       </c>
-      <c r="E66" t="s">
-        <v>323</v>
-      </c>
       <c r="F66" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -6879,13 +6983,13 @@
         <v>237</v>
       </c>
       <c r="D67" t="s">
+        <v>323</v>
+      </c>
+      <c r="E67" t="s">
         <v>324</v>
       </c>
-      <c r="E67" t="s">
-        <v>325</v>
-      </c>
       <c r="F67" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -6899,13 +7003,13 @@
         <v>237</v>
       </c>
       <c r="D68" t="s">
+        <v>325</v>
+      </c>
+      <c r="E68" t="s">
         <v>326</v>
       </c>
-      <c r="E68" t="s">
-        <v>327</v>
-      </c>
       <c r="F68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -6919,25 +7023,25 @@
         <v>237</v>
       </c>
       <c r="D69" t="s">
+        <v>327</v>
+      </c>
+      <c r="E69" t="s">
         <v>328</v>
       </c>
-      <c r="E69" t="s">
-        <v>329</v>
-      </c>
       <c r="F69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -6951,25 +7055,25 @@
         <v>237</v>
       </c>
       <c r="D70" t="s">
+        <v>329</v>
+      </c>
+      <c r="E70" t="s">
         <v>330</v>
       </c>
-      <c r="E70" t="s">
-        <v>331</v>
-      </c>
       <c r="F70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -6983,25 +7087,25 @@
         <v>237</v>
       </c>
       <c r="D71" t="s">
+        <v>331</v>
+      </c>
+      <c r="E71" t="s">
         <v>332</v>
       </c>
-      <c r="E71" t="s">
-        <v>333</v>
-      </c>
       <c r="F71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -7015,25 +7119,25 @@
         <v>237</v>
       </c>
       <c r="D72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" t="s">
         <v>334</v>
       </c>
-      <c r="E72" t="s">
-        <v>335</v>
-      </c>
       <c r="F72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -7047,25 +7151,25 @@
         <v>237</v>
       </c>
       <c r="D73" t="s">
+        <v>335</v>
+      </c>
+      <c r="E73" t="s">
         <v>336</v>
       </c>
-      <c r="E73" t="s">
-        <v>337</v>
-      </c>
       <c r="F73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -7079,25 +7183,25 @@
         <v>237</v>
       </c>
       <c r="D74" t="s">
+        <v>337</v>
+      </c>
+      <c r="E74" t="s">
         <v>338</v>
       </c>
-      <c r="E74" t="s">
-        <v>339</v>
-      </c>
       <c r="F74" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G74" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H74" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I74" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J74" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -7108,28 +7212,28 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D75" t="s">
+        <v>388</v>
+      </c>
+      <c r="E75" t="s">
         <v>389</v>
       </c>
-      <c r="E75" t="s">
-        <v>390</v>
-      </c>
       <c r="F75" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G75" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H75" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I75" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J75" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -7140,28 +7244,28 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D76" t="s">
+        <v>390</v>
+      </c>
+      <c r="E76" t="s">
         <v>391</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>392</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>393</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>394</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>395</v>
       </c>
-      <c r="I76" t="s">
-        <v>396</v>
-      </c>
       <c r="J76" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -7172,28 +7276,28 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D77" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E77" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F77" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G77" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H77" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I77" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J77" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -7204,28 +7308,28 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E78" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F78" t="s">
+        <v>392</v>
+      </c>
+      <c r="G78" t="s">
         <v>393</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>394</v>
       </c>
-      <c r="H78" t="s">
-        <v>395</v>
-      </c>
       <c r="I78" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J78" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -7236,28 +7340,28 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D79" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E79" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F79" t="s">
+        <v>392</v>
+      </c>
+      <c r="G79" t="s">
         <v>393</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>394</v>
       </c>
-      <c r="H79" t="s">
-        <v>395</v>
-      </c>
       <c r="I79" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J79" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -7268,28 +7372,28 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E80" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F80" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G80" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H80" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J80" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,28 +7404,28 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D81" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E81" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F81" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G81" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H81" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I81" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J81" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -7332,28 +7436,28 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D82" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E82" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F82" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G82" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H82" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I82" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J82" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -7364,28 +7468,28 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E83" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F83" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G83" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H83" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I83" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J83" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -7396,28 +7500,28 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E84" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F84" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G84" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H84" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I84" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J84" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -7428,28 +7532,28 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D85" t="s">
+        <v>427</v>
+      </c>
+      <c r="E85" t="s">
         <v>428</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>392</v>
+      </c>
+      <c r="G85" t="s">
+        <v>393</v>
+      </c>
+      <c r="H85" t="s">
+        <v>401</v>
+      </c>
+      <c r="I85" t="s">
         <v>429</v>
       </c>
-      <c r="F85" t="s">
-        <v>393</v>
-      </c>
-      <c r="G85" t="s">
-        <v>394</v>
-      </c>
-      <c r="H85" t="s">
-        <v>402</v>
-      </c>
-      <c r="I85" t="s">
-        <v>430</v>
-      </c>
       <c r="J85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -7460,28 +7564,28 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D86" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E86" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F86" t="s">
+        <v>392</v>
+      </c>
+      <c r="G86" t="s">
         <v>393</v>
       </c>
-      <c r="G86" t="s">
-        <v>394</v>
-      </c>
       <c r="H86" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I86" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J86" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -7492,28 +7596,28 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D87" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E87" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F87" t="s">
+        <v>392</v>
+      </c>
+      <c r="G87" t="s">
         <v>393</v>
       </c>
-      <c r="G87" t="s">
-        <v>394</v>
-      </c>
       <c r="H87" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I87" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J87" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -7524,28 +7628,28 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D88" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E88" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F88" t="s">
+        <v>392</v>
+      </c>
+      <c r="G88" t="s">
         <v>393</v>
       </c>
-      <c r="G88" t="s">
-        <v>394</v>
-      </c>
       <c r="H88" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I88" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J88" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -7556,28 +7660,28 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D89" t="s">
+        <v>327</v>
+      </c>
+      <c r="E89" t="s">
         <v>328</v>
       </c>
-      <c r="E89" t="s">
-        <v>329</v>
-      </c>
       <c r="F89" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -7588,28 +7692,28 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D90" t="s">
+        <v>329</v>
+      </c>
+      <c r="E90" t="s">
         <v>330</v>
       </c>
-      <c r="E90" t="s">
-        <v>331</v>
-      </c>
       <c r="F90" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G90" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H90" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I90" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J90" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -7620,28 +7724,28 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D91" t="s">
+        <v>331</v>
+      </c>
+      <c r="E91" t="s">
         <v>332</v>
       </c>
-      <c r="E91" t="s">
-        <v>333</v>
-      </c>
       <c r="F91" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G91" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H91" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I91" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J91" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -7652,28 +7756,28 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D92" t="s">
+        <v>333</v>
+      </c>
+      <c r="E92" t="s">
         <v>334</v>
       </c>
-      <c r="E92" t="s">
-        <v>335</v>
-      </c>
       <c r="F92" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G92" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H92" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I92" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J92" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -7684,28 +7788,28 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D93" t="s">
+        <v>335</v>
+      </c>
+      <c r="E93" t="s">
         <v>336</v>
       </c>
-      <c r="E93" t="s">
-        <v>337</v>
-      </c>
       <c r="F93" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G93" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H93" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I93" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J93" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -7716,28 +7820,28 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D94" t="s">
+        <v>337</v>
+      </c>
+      <c r="E94" t="s">
         <v>338</v>
       </c>
-      <c r="E94" t="s">
-        <v>339</v>
-      </c>
       <c r="F94" t="s">
+        <v>392</v>
+      </c>
+      <c r="G94" t="s">
         <v>393</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>394</v>
       </c>
-      <c r="H94" t="s">
-        <v>395</v>
-      </c>
       <c r="I94" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J94" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -7748,28 +7852,28 @@
         <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D95" t="s">
+        <v>440</v>
+      </c>
+      <c r="E95" t="s">
         <v>441</v>
       </c>
-      <c r="E95" t="s">
-        <v>442</v>
-      </c>
       <c r="F95" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G95" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H95" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I95" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J95" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -7780,28 +7884,28 @@
         <v>80</v>
       </c>
       <c r="C96" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D96" t="s">
+        <v>442</v>
+      </c>
+      <c r="E96" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" t="s">
+        <v>392</v>
+      </c>
+      <c r="G96" t="s">
+        <v>438</v>
+      </c>
+      <c r="H96" t="s">
+        <v>438</v>
+      </c>
+      <c r="I96" t="s">
+        <v>438</v>
+      </c>
+      <c r="J96" t="s">
         <v>443</v>
-      </c>
-      <c r="E96" t="s">
-        <v>289</v>
-      </c>
-      <c r="F96" t="s">
-        <v>439</v>
-      </c>
-      <c r="G96" t="s">
-        <v>439</v>
-      </c>
-      <c r="H96" t="s">
-        <v>439</v>
-      </c>
-      <c r="I96" t="s">
-        <v>439</v>
-      </c>
-      <c r="J96" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -7812,25 +7916,25 @@
         <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F97" t="s">
+        <v>392</v>
+      </c>
+      <c r="G97" t="s">
         <v>393</v>
       </c>
-      <c r="G97" t="s">
-        <v>394</v>
-      </c>
       <c r="H97" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I97" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -7841,25 +7945,25 @@
         <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E98" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F98" t="s">
+        <v>392</v>
+      </c>
+      <c r="G98" t="s">
         <v>393</v>
       </c>
-      <c r="G98" t="s">
-        <v>394</v>
-      </c>
       <c r="H98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I98" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -7870,25 +7974,25 @@
         <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E99" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F99" t="s">
+        <v>392</v>
+      </c>
+      <c r="G99" t="s">
         <v>393</v>
       </c>
-      <c r="G99" t="s">
-        <v>394</v>
-      </c>
       <c r="H99" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I99" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -7899,25 +8003,25 @@
         <v>80</v>
       </c>
       <c r="C100" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D100" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="E100" t="s">
         <v>473</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
+        <v>392</v>
+      </c>
+      <c r="G100" t="s">
+        <v>400</v>
+      </c>
+      <c r="H100" t="s">
         <v>474</v>
       </c>
-      <c r="F100" t="s">
-        <v>393</v>
-      </c>
-      <c r="G100" t="s">
-        <v>401</v>
-      </c>
-      <c r="H100" t="s">
-        <v>475</v>
-      </c>
       <c r="I100" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -7928,25 +8032,25 @@
         <v>80</v>
       </c>
       <c r="C101" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D101" t="s">
+        <v>327</v>
+      </c>
+      <c r="E101" t="s">
         <v>328</v>
       </c>
-      <c r="E101" t="s">
-        <v>329</v>
-      </c>
       <c r="F101" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -7957,25 +8061,25 @@
         <v>80</v>
       </c>
       <c r="C102" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D102" t="s">
+        <v>329</v>
+      </c>
+      <c r="E102" t="s">
         <v>330</v>
       </c>
-      <c r="E102" t="s">
-        <v>331</v>
-      </c>
       <c r="F102" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G102" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H102" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I102" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -7986,25 +8090,25 @@
         <v>80</v>
       </c>
       <c r="C103" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D103" t="s">
+        <v>331</v>
+      </c>
+      <c r="E103" t="s">
         <v>332</v>
       </c>
-      <c r="E103" t="s">
-        <v>333</v>
-      </c>
       <c r="F103" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G103" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H103" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I103" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -8015,25 +8119,25 @@
         <v>80</v>
       </c>
       <c r="C104" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D104" t="s">
+        <v>333</v>
+      </c>
+      <c r="E104" t="s">
         <v>334</v>
       </c>
-      <c r="E104" t="s">
-        <v>335</v>
-      </c>
       <c r="F104" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G104" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H104" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I104" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -8044,25 +8148,25 @@
         <v>80</v>
       </c>
       <c r="C105" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D105" t="s">
+        <v>335</v>
+      </c>
+      <c r="E105" t="s">
         <v>336</v>
       </c>
-      <c r="E105" t="s">
-        <v>337</v>
-      </c>
       <c r="F105" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G105" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H105" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I105" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -8073,28 +8177,28 @@
         <v>80</v>
       </c>
       <c r="C106" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D106" t="s">
+        <v>337</v>
+      </c>
+      <c r="E106" t="s">
         <v>338</v>
       </c>
-      <c r="E106" t="s">
-        <v>339</v>
-      </c>
       <c r="F106" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J106" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -8105,25 +8209,25 @@
         <v>80</v>
       </c>
       <c r="C107" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D107" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E107" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F107" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="G107" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H107" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I107" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -8134,25 +8238,25 @@
         <v>80</v>
       </c>
       <c r="C108" t="s">
+        <v>475</v>
+      </c>
+      <c r="D108" t="s">
         <v>477</v>
       </c>
-      <c r="D108" t="s">
-        <v>479</v>
-      </c>
       <c r="E108" t="s">
+        <v>428</v>
+      </c>
+      <c r="F108" t="s">
+        <v>392</v>
+      </c>
+      <c r="G108" t="s">
+        <v>393</v>
+      </c>
+      <c r="H108" t="s">
+        <v>401</v>
+      </c>
+      <c r="I108" t="s">
         <v>429</v>
-      </c>
-      <c r="F108" t="s">
-        <v>393</v>
-      </c>
-      <c r="G108" t="s">
-        <v>394</v>
-      </c>
-      <c r="H108" t="s">
-        <v>402</v>
-      </c>
-      <c r="I108" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -8163,25 +8267,25 @@
         <v>80</v>
       </c>
       <c r="C109" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D109" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E109" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F109" t="s">
+        <v>392</v>
+      </c>
+      <c r="G109" t="s">
         <v>393</v>
       </c>
-      <c r="G109" t="s">
-        <v>394</v>
-      </c>
       <c r="H109" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I109" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -8192,25 +8296,25 @@
         <v>80</v>
       </c>
       <c r="C110" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D110" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E110" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F110" t="s">
+        <v>392</v>
+      </c>
+      <c r="G110" t="s">
         <v>393</v>
       </c>
-      <c r="G110" t="s">
-        <v>394</v>
-      </c>
       <c r="H110" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I110" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -8221,25 +8325,25 @@
         <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D111" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E111" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F111" t="s">
+        <v>392</v>
+      </c>
+      <c r="G111" t="s">
         <v>393</v>
       </c>
-      <c r="G111" t="s">
-        <v>394</v>
-      </c>
       <c r="H111" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I111" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8250,25 +8354,25 @@
         <v>80</v>
       </c>
       <c r="C112" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D112" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E112" t="s">
+        <v>486</v>
+      </c>
+      <c r="F112" t="s">
+        <v>392</v>
+      </c>
+      <c r="G112" t="s">
+        <v>393</v>
+      </c>
+      <c r="H112" t="s">
+        <v>401</v>
+      </c>
+      <c r="I112" t="s">
         <v>488</v>
-      </c>
-      <c r="F112" t="s">
-        <v>393</v>
-      </c>
-      <c r="G112" t="s">
-        <v>394</v>
-      </c>
-      <c r="H112" t="s">
-        <v>402</v>
-      </c>
-      <c r="I112" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -8279,25 +8383,25 @@
         <v>80</v>
       </c>
       <c r="C113" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D113" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E113" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F113" t="s">
+        <v>392</v>
+      </c>
+      <c r="G113" t="s">
         <v>393</v>
       </c>
-      <c r="G113" t="s">
-        <v>394</v>
-      </c>
       <c r="H113" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I113" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8308,25 +8412,25 @@
         <v>80</v>
       </c>
       <c r="C114" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D114" t="s">
+        <v>327</v>
+      </c>
+      <c r="E114" t="s">
         <v>328</v>
       </c>
-      <c r="E114" t="s">
-        <v>329</v>
-      </c>
       <c r="F114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -8337,25 +8441,25 @@
         <v>80</v>
       </c>
       <c r="C115" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D115" t="s">
+        <v>329</v>
+      </c>
+      <c r="E115" t="s">
         <v>330</v>
       </c>
-      <c r="E115" t="s">
-        <v>331</v>
-      </c>
       <c r="F115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -8366,25 +8470,25 @@
         <v>80</v>
       </c>
       <c r="C116" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D116" t="s">
+        <v>331</v>
+      </c>
+      <c r="E116" t="s">
         <v>332</v>
       </c>
-      <c r="E116" t="s">
-        <v>333</v>
-      </c>
       <c r="F116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -8395,25 +8499,25 @@
         <v>80</v>
       </c>
       <c r="C117" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D117" t="s">
+        <v>333</v>
+      </c>
+      <c r="E117" t="s">
         <v>334</v>
       </c>
-      <c r="E117" t="s">
-        <v>335</v>
-      </c>
       <c r="F117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -8424,25 +8528,25 @@
         <v>80</v>
       </c>
       <c r="C118" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D118" t="s">
+        <v>335</v>
+      </c>
+      <c r="E118" t="s">
         <v>336</v>
       </c>
-      <c r="E118" t="s">
-        <v>337</v>
-      </c>
       <c r="F118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -8453,28 +8557,28 @@
         <v>80</v>
       </c>
       <c r="C119" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D119" t="s">
+        <v>337</v>
+      </c>
+      <c r="E119" t="s">
         <v>338</v>
       </c>
-      <c r="E119" t="s">
-        <v>339</v>
-      </c>
       <c r="F119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J119" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -8485,13 +8589,16 @@
         <v>80</v>
       </c>
       <c r="C120" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D120" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E120" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="F120" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8502,10 +8609,13 @@
         <v>80</v>
       </c>
       <c r="C121" t="s">
+        <v>489</v>
+      </c>
+      <c r="D121" t="s">
         <v>491</v>
       </c>
-      <c r="D121" t="s">
-        <v>493</v>
+      <c r="F121" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -8516,10 +8626,16 @@
         <v>80</v>
       </c>
       <c r="C122" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D122" t="s">
-        <v>494</v>
+        <v>492</v>
+      </c>
+      <c r="E122" t="s">
+        <v>499</v>
+      </c>
+      <c r="F122" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8530,10 +8646,13 @@
         <v>80</v>
       </c>
       <c r="C123" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D123" t="s">
-        <v>495</v>
+        <v>493</v>
+      </c>
+      <c r="F123" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -8544,10 +8663,13 @@
         <v>80</v>
       </c>
       <c r="C124" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D124" t="s">
-        <v>496</v>
+        <v>494</v>
+      </c>
+      <c r="F124" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -8558,10 +8680,13 @@
         <v>80</v>
       </c>
       <c r="C125" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D125" t="s">
-        <v>497</v>
+        <v>495</v>
+      </c>
+      <c r="F125" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -8572,16 +8697,25 @@
         <v>80</v>
       </c>
       <c r="C126" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D126" t="s">
+        <v>327</v>
+      </c>
+      <c r="E126" t="s">
         <v>328</v>
       </c>
-      <c r="E126" t="s">
-        <v>329</v>
-      </c>
       <c r="F126" t="s">
-        <v>439</v>
+        <v>438</v>
+      </c>
+      <c r="G126" t="s">
+        <v>438</v>
+      </c>
+      <c r="H126" t="s">
+        <v>438</v>
+      </c>
+      <c r="I126" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -8592,16 +8726,25 @@
         <v>80</v>
       </c>
       <c r="C127" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D127" t="s">
+        <v>329</v>
+      </c>
+      <c r="E127" t="s">
         <v>330</v>
       </c>
-      <c r="E127" t="s">
-        <v>331</v>
-      </c>
       <c r="F127" t="s">
-        <v>439</v>
+        <v>438</v>
+      </c>
+      <c r="G127" t="s">
+        <v>438</v>
+      </c>
+      <c r="H127" t="s">
+        <v>438</v>
+      </c>
+      <c r="I127" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -8612,89 +8755,664 @@
         <v>80</v>
       </c>
       <c r="C128" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D128" t="s">
+        <v>331</v>
+      </c>
+      <c r="E128" t="s">
         <v>332</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
+        <v>438</v>
+      </c>
+      <c r="G128" t="s">
+        <v>438</v>
+      </c>
+      <c r="H128" t="s">
+        <v>438</v>
+      </c>
+      <c r="I128" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>235</v>
+      </c>
+      <c r="B129" t="s">
+        <v>80</v>
+      </c>
+      <c r="C129" t="s">
+        <v>489</v>
+      </c>
+      <c r="D129" t="s">
         <v>333</v>
       </c>
-      <c r="F128" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>235</v>
-      </c>
-      <c r="B129" t="s">
-        <v>80</v>
-      </c>
-      <c r="C129" t="s">
-        <v>491</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>334</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
+        <v>438</v>
+      </c>
+      <c r="G129" t="s">
+        <v>438</v>
+      </c>
+      <c r="H129" t="s">
+        <v>438</v>
+      </c>
+      <c r="I129" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>235</v>
+      </c>
+      <c r="B130" t="s">
+        <v>80</v>
+      </c>
+      <c r="C130" t="s">
+        <v>489</v>
+      </c>
+      <c r="D130" t="s">
         <v>335</v>
       </c>
-      <c r="F129" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>235</v>
-      </c>
-      <c r="B130" t="s">
-        <v>80</v>
-      </c>
-      <c r="C130" t="s">
-        <v>491</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>336</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
+        <v>438</v>
+      </c>
+      <c r="G130" t="s">
+        <v>438</v>
+      </c>
+      <c r="H130" t="s">
+        <v>438</v>
+      </c>
+      <c r="I130" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>235</v>
+      </c>
+      <c r="B131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131" t="s">
+        <v>489</v>
+      </c>
+      <c r="D131" t="s">
         <v>337</v>
       </c>
-      <c r="F130" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>235</v>
-      </c>
-      <c r="B131" t="s">
-        <v>80</v>
-      </c>
-      <c r="C131" t="s">
-        <v>491</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>338</v>
       </c>
-      <c r="E131" t="s">
-        <v>339</v>
-      </c>
       <c r="F131" t="s">
-        <v>439</v>
+        <v>438</v>
+      </c>
+      <c r="G131" t="s">
+        <v>438</v>
+      </c>
+      <c r="H131" t="s">
+        <v>438</v>
+      </c>
+      <c r="I131" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>234</v>
+      </c>
+      <c r="B132" t="s">
+        <v>82</v>
+      </c>
+      <c r="C132" t="s">
+        <v>496</v>
+      </c>
+      <c r="D132" t="s">
+        <v>500</v>
+      </c>
+      <c r="E132" t="s">
+        <v>501</v>
+      </c>
+      <c r="F132" t="s">
+        <v>392</v>
+      </c>
+      <c r="G132" t="s">
+        <v>393</v>
+      </c>
+      <c r="H132" t="s">
+        <v>503</v>
+      </c>
+      <c r="I132" t="s">
+        <v>504</v>
+      </c>
+      <c r="J132" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>234</v>
+      </c>
+      <c r="B133" t="s">
+        <v>82</v>
+      </c>
+      <c r="C133" t="s">
+        <v>496</v>
+      </c>
+      <c r="D133" t="s">
+        <v>505</v>
+      </c>
+      <c r="E133" t="s">
+        <v>507</v>
+      </c>
+      <c r="F133" t="s">
+        <v>392</v>
+      </c>
+      <c r="G133" t="s">
+        <v>393</v>
+      </c>
+      <c r="H133" t="s">
+        <v>503</v>
+      </c>
+      <c r="I133" t="s">
+        <v>506</v>
+      </c>
+      <c r="J133" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>234</v>
+      </c>
+      <c r="B134" t="s">
+        <v>82</v>
+      </c>
+      <c r="C134" t="s">
+        <v>496</v>
+      </c>
+      <c r="D134" t="s">
+        <v>240</v>
+      </c>
+      <c r="E134" t="s">
+        <v>512</v>
+      </c>
+      <c r="F134" t="s">
+        <v>392</v>
+      </c>
+      <c r="G134" t="s">
+        <v>393</v>
+      </c>
+      <c r="H134" t="s">
+        <v>511</v>
+      </c>
+      <c r="I134" t="s">
+        <v>508</v>
+      </c>
+      <c r="J134" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>234</v>
+      </c>
+      <c r="B135" t="s">
+        <v>82</v>
+      </c>
+      <c r="C135" t="s">
+        <v>496</v>
+      </c>
+      <c r="D135" t="s">
+        <v>518</v>
+      </c>
+      <c r="E135" t="s">
+        <v>513</v>
+      </c>
+      <c r="F135" t="s">
+        <v>392</v>
+      </c>
+      <c r="G135" t="s">
+        <v>393</v>
+      </c>
+      <c r="H135" t="s">
+        <v>511</v>
+      </c>
+      <c r="I135" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>234</v>
+      </c>
+      <c r="B136" t="s">
+        <v>82</v>
+      </c>
+      <c r="C136" t="s">
+        <v>496</v>
+      </c>
+      <c r="D136" t="s">
+        <v>388</v>
+      </c>
+      <c r="E136" t="s">
+        <v>514</v>
+      </c>
+      <c r="F136" t="s">
+        <v>392</v>
+      </c>
+      <c r="G136" t="s">
+        <v>393</v>
+      </c>
+      <c r="H136" t="s">
+        <v>511</v>
+      </c>
+      <c r="I136" t="s">
+        <v>403</v>
+      </c>
+      <c r="J136" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
+        <v>82</v>
+      </c>
+      <c r="C137" t="s">
+        <v>496</v>
+      </c>
+      <c r="D137" t="s">
+        <v>490</v>
+      </c>
+      <c r="E137" t="s">
+        <v>515</v>
+      </c>
+      <c r="F137" t="s">
+        <v>392</v>
+      </c>
+      <c r="G137" t="s">
+        <v>393</v>
+      </c>
+      <c r="H137" t="s">
+        <v>511</v>
+      </c>
+      <c r="I137" t="s">
+        <v>510</v>
+      </c>
+      <c r="J137" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>234</v>
+      </c>
+      <c r="B138" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" t="s">
+        <v>496</v>
+      </c>
+      <c r="D138" t="s">
+        <v>442</v>
+      </c>
+      <c r="E138" t="s">
+        <v>516</v>
+      </c>
+      <c r="F138" t="s">
+        <v>392</v>
+      </c>
+      <c r="G138" t="s">
+        <v>393</v>
+      </c>
+      <c r="H138" t="s">
+        <v>511</v>
+      </c>
+      <c r="I138" t="s">
+        <v>406</v>
+      </c>
+      <c r="J138" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>234</v>
+      </c>
+      <c r="B139" t="s">
+        <v>82</v>
+      </c>
+      <c r="C139" t="s">
+        <v>496</v>
+      </c>
+      <c r="D139" t="s">
+        <v>287</v>
+      </c>
+      <c r="E139" t="s">
+        <v>519</v>
+      </c>
+      <c r="F139" t="s">
+        <v>497</v>
+      </c>
+      <c r="G139" t="s">
+        <v>393</v>
+      </c>
+      <c r="H139" t="s">
+        <v>503</v>
+      </c>
+      <c r="I139" t="s">
+        <v>517</v>
+      </c>
+      <c r="J139" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>234</v>
+      </c>
+      <c r="B140" t="s">
+        <v>82</v>
+      </c>
+      <c r="C140" t="s">
+        <v>496</v>
+      </c>
+      <c r="D140" t="s">
+        <v>528</v>
+      </c>
+      <c r="E140" t="s">
+        <v>524</v>
+      </c>
+      <c r="F140" t="s">
+        <v>392</v>
+      </c>
+      <c r="G140" t="s">
+        <v>393</v>
+      </c>
+      <c r="H140" t="s">
+        <v>503</v>
+      </c>
+      <c r="I140" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>234</v>
+      </c>
+      <c r="B141" t="s">
+        <v>82</v>
+      </c>
+      <c r="C141" t="s">
+        <v>496</v>
+      </c>
+      <c r="D141" t="s">
+        <v>529</v>
+      </c>
+      <c r="E141" t="s">
+        <v>525</v>
+      </c>
+      <c r="F141" t="s">
+        <v>392</v>
+      </c>
+      <c r="G141" t="s">
+        <v>393</v>
+      </c>
+      <c r="H141" t="s">
+        <v>503</v>
+      </c>
+      <c r="I141" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>234</v>
+      </c>
+      <c r="B142" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" t="s">
+        <v>496</v>
+      </c>
+      <c r="D142" t="s">
+        <v>530</v>
+      </c>
+      <c r="E142" t="s">
+        <v>526</v>
+      </c>
+      <c r="F142" t="s">
+        <v>392</v>
+      </c>
+      <c r="G142" t="s">
+        <v>393</v>
+      </c>
+      <c r="H142" t="s">
+        <v>503</v>
+      </c>
+      <c r="I142" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>234</v>
+      </c>
+      <c r="B143" t="s">
+        <v>82</v>
+      </c>
+      <c r="C143" t="s">
+        <v>496</v>
+      </c>
+      <c r="D143" t="s">
+        <v>531</v>
+      </c>
+      <c r="E143" t="s">
+        <v>527</v>
+      </c>
+      <c r="F143" t="s">
+        <v>392</v>
+      </c>
+      <c r="G143" t="s">
+        <v>393</v>
+      </c>
+      <c r="H143" t="s">
+        <v>503</v>
+      </c>
+      <c r="I143" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>234</v>
+      </c>
+      <c r="B144" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" t="s">
+        <v>496</v>
+      </c>
+      <c r="D144" t="s">
+        <v>327</v>
+      </c>
+      <c r="E144" t="s">
+        <v>328</v>
+      </c>
+      <c r="F144" t="s">
+        <v>438</v>
+      </c>
+      <c r="G144" t="s">
+        <v>438</v>
+      </c>
+      <c r="H144" t="s">
+        <v>438</v>
+      </c>
+      <c r="I144" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>234</v>
+      </c>
+      <c r="B145" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" t="s">
+        <v>496</v>
+      </c>
+      <c r="D145" t="s">
+        <v>329</v>
+      </c>
+      <c r="E145" t="s">
+        <v>330</v>
+      </c>
+      <c r="F145" t="s">
+        <v>438</v>
+      </c>
+      <c r="G145" t="s">
+        <v>438</v>
+      </c>
+      <c r="H145" t="s">
+        <v>438</v>
+      </c>
+      <c r="I145" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>234</v>
+      </c>
+      <c r="B146" t="s">
+        <v>82</v>
+      </c>
+      <c r="C146" t="s">
+        <v>496</v>
+      </c>
+      <c r="D146" t="s">
+        <v>331</v>
+      </c>
+      <c r="E146" t="s">
+        <v>332</v>
+      </c>
+      <c r="F146" t="s">
+        <v>438</v>
+      </c>
+      <c r="G146" t="s">
+        <v>438</v>
+      </c>
+      <c r="H146" t="s">
+        <v>438</v>
+      </c>
+      <c r="I146" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>234</v>
+      </c>
+      <c r="B147" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" t="s">
+        <v>496</v>
+      </c>
+      <c r="D147" t="s">
+        <v>333</v>
+      </c>
+      <c r="E147" t="s">
+        <v>334</v>
+      </c>
+      <c r="F147" t="s">
+        <v>438</v>
+      </c>
+      <c r="G147" t="s">
+        <v>438</v>
+      </c>
+      <c r="H147" t="s">
+        <v>438</v>
+      </c>
+      <c r="I147" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>234</v>
+      </c>
+      <c r="B148" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" t="s">
+        <v>496</v>
+      </c>
+      <c r="D148" t="s">
+        <v>335</v>
+      </c>
+      <c r="E148" t="s">
+        <v>336</v>
+      </c>
+      <c r="F148" t="s">
+        <v>438</v>
+      </c>
+      <c r="G148" t="s">
+        <v>438</v>
+      </c>
+      <c r="H148" t="s">
+        <v>438</v>
+      </c>
+      <c r="I148" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>234</v>
+      </c>
+      <c r="B149" t="s">
+        <v>82</v>
+      </c>
+      <c r="C149" t="s">
+        <v>496</v>
+      </c>
+      <c r="D149" t="s">
+        <v>337</v>
+      </c>
+      <c r="E149" t="s">
+        <v>338</v>
+      </c>
+      <c r="F149" t="s">
+        <v>438</v>
+      </c>
+      <c r="G149" t="s">
+        <v>438</v>
+      </c>
+      <c r="H149" t="s">
+        <v>438</v>
+      </c>
+      <c r="I149" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F114:F115">
-    <cfRule type="expression" dxfId="1" priority="1432">
-      <formula>AND($A113&lt;&gt;"", MOD(ROW(),2) = 0)</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A131" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A149" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>SchemaList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B131" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B149" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>ObjectTypeList</formula1>
     </dataValidation>
   </dataValidations>
@@ -8742,54 +9460,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="100" t="s">
+      <c r="D1" s="99"/>
+      <c r="E1" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="104" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="105"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="104" t="s">
+      <c r="I1" s="103"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="104" t="s">
+      <c r="L1" s="104"/>
+      <c r="M1" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="98"/>
+      <c r="N1" s="96"/>
       <c r="O1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="104" t="s">
+      <c r="P1" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="100" t="s">
+      <c r="Q1" s="104"/>
+      <c r="R1" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="98" t="s">
+      <c r="S1" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="98" t="s">
+      <c r="T1" s="96" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="108"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="106"/>
       <c r="C2" s="11" t="s">
         <v>29</v>
       </c>
@@ -8835,9 +9553,9 @@
       <c r="Q2" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="109"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
@@ -8943,19 +9661,19 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="91" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E2" s="92" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G2,FIND("]",G2)),"]",""),"[",""),"    ","")</f>
         <v>territory_key</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M2" s="87"/>
       <c r="N2" s="88"/>
@@ -8970,17 +9688,17 @@
         <v>1</v>
       </c>
       <c r="C3" s="83" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D3" s="83" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E3" s="92" t="str">
         <f t="shared" ref="E3:E6" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G3,FIND("]",G3)),"]",""),"[",""),"    ","")</f>
         <v>territory_name_bk</v>
       </c>
       <c r="G3" s="83" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q3" s="87"/>
       <c r="R3" s="88"/>
@@ -8995,17 +9713,17 @@
         <v>2</v>
       </c>
       <c r="C4" s="83" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D4" s="83" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E4" s="92" t="str">
         <f t="shared" si="0"/>
         <v>territory_group</v>
       </c>
       <c r="G4" s="83" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q4" s="87"/>
       <c r="R4" s="88"/>
@@ -9020,17 +9738,17 @@
         <v>3</v>
       </c>
       <c r="C5" s="84" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D5" s="83" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E5" s="92" t="str">
         <f t="shared" si="0"/>
         <v>country_region_code</v>
       </c>
       <c r="G5" s="83" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q5" s="87"/>
       <c r="R5" s="88"/>
@@ -9045,17 +9763,17 @@
         <v>4</v>
       </c>
       <c r="C6" s="83" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E6" s="92" t="str">
         <f t="shared" si="0"/>
         <v>country_name</v>
       </c>
       <c r="G6" s="83" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q6" s="87"/>
       <c r="R6" s="88"/>
@@ -9067,13 +9785,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="83" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" s="83" t="s">
         <v>446</v>
       </c>
-      <c r="D7" s="83" t="s">
-        <v>447</v>
-      </c>
       <c r="G7" s="83" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q7" s="87"/>
       <c r="R7" s="88"/>
@@ -9085,17 +9803,17 @@
         <v>6</v>
       </c>
       <c r="C8" s="83" t="s">
+        <v>447</v>
+      </c>
+      <c r="D8" s="83" t="s">
         <v>448</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>449</v>
       </c>
       <c r="E8" s="83" t="str">
         <f t="shared" ref="E8:E12" si="1">LEFT(G8, FIND("]", G8))</f>
         <v>    [sys_insert_date]</v>
       </c>
       <c r="G8" s="83" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q8" s="87"/>
       <c r="R8" s="88"/>
@@ -9107,17 +9825,17 @@
         <v>7</v>
       </c>
       <c r="C9" s="83" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" s="83" t="s">
         <v>450</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>451</v>
       </c>
       <c r="E9" s="83" t="str">
         <f t="shared" si="1"/>
         <v>    [sys_update_date]</v>
       </c>
       <c r="G9" s="83" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N9" s="87"/>
       <c r="O9" s="88"/>
@@ -9129,17 +9847,17 @@
         <v>8</v>
       </c>
       <c r="C10" s="83" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="83" t="s">
         <v>452</v>
-      </c>
-      <c r="D10" s="83" t="s">
-        <v>453</v>
       </c>
       <c r="E10" s="83" t="str">
         <f t="shared" si="1"/>
         <v>    [sys_delete_date]</v>
       </c>
       <c r="G10" s="83" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N10" s="87"/>
       <c r="O10" s="88"/>
@@ -9151,17 +9869,17 @@
         <v>9</v>
       </c>
       <c r="C11" s="83" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="83" t="s">
         <v>454</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>455</v>
       </c>
       <c r="E11" s="83" t="str">
         <f t="shared" si="1"/>
         <v>    [sys_hash_value]</v>
       </c>
       <c r="G11" s="83" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N11" s="87"/>
       <c r="O11" s="88"/>
@@ -9173,17 +9891,17 @@
         <v>10</v>
       </c>
       <c r="C12" s="83" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="83" t="s">
         <v>456</v>
-      </c>
-      <c r="D12" s="83" t="s">
-        <v>457</v>
       </c>
       <c r="E12" s="83" t="str">
         <f t="shared" si="1"/>
         <v>    [sys_data_source]</v>
       </c>
       <c r="G12" s="83" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N12" s="87"/>
       <c r="O12" s="88"/>
@@ -9192,7 +9910,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="84"/>
       <c r="G13" s="83" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N13" s="87"/>
       <c r="O13" s="88"/>

--- a/docs/enterprise_data_warehouse_bus_matrix.xlsx
+++ b/docs/enterprise_data_warehouse_bus_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahdi\Documents\GitHub\dwh-adventureworks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1DB6C9-67D3-44A1-8CA6-ED2252BCC022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D01E15A-DFBC-4E75-BA9A-9901F1356641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definitions" sheetId="2" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="506">
   <si>
     <t>Story Point Values</t>
   </si>
@@ -1416,87 +1416,6 @@
     <t>Data warehouse Primary Key.</t>
   </si>
   <si>
-    <t>Primary key for SalesTerritory records.</t>
-  </si>
-  <si>
-    <t>SalesYTD</t>
-  </si>
-  <si>
-    <t>Sales in the territory year to date.</t>
-  </si>
-  <si>
-    <t>SalesLastYear</t>
-  </si>
-  <si>
-    <t>Sales in the territory the previous year.</t>
-  </si>
-  <si>
-    <t>CostYTD</t>
-  </si>
-  <si>
-    <t>Business costs in the territory year to date.</t>
-  </si>
-  <si>
-    <t>CostLastYear</t>
-  </si>
-  <si>
-    <t>Business costs in the territory the previous year.</t>
-  </si>
-  <si>
-    <t>rowguid</t>
-  </si>
-  <si>
-    <t>ROWGUIDCOL number uniquely identifying the record. Used to support a merge replication sample.</t>
-  </si>
-  <si>
-    <t>ModifiedDate</t>
-  </si>
-  <si>
-    <t>Date and time the record was last updated.</t>
-  </si>
-  <si>
-    <t>-- System metadata attributes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    [sys_source_record_id] </t>
-  </si>
-  <si>
-    <t>    [territory_name_bk]         NVARCHAR (20)       NOT NULL,   --</t>
-  </si>
-  <si>
-    <t>    [territory_group]           NVARCHAR (20)       NOT NULL,</t>
-  </si>
-  <si>
-    <t>    [country_region_code]       NVARCHAR (5)        NOT NULL,</t>
-  </si>
-  <si>
-    <t>    [country_name]              NVARCHAR (30)       NOT NULL,</t>
-  </si>
-  <si>
-    <t>    [sys_insert_date]         DATETIME2(3)        NOT NULL,   -- System metadata: date and time when the record was inserted.</t>
-  </si>
-  <si>
-    <t>    [sys_update_date]         DATETIME2(3)            NULL,   -- System metadata: date and time when the record was last updated.</t>
-  </si>
-  <si>
-    <t>    [sys_delete_date]         DATETIME2(3)            NULL,   -- System metadata: date and time when the record was deleted or marked for deletion.</t>
-  </si>
-  <si>
-    <t>    [sys_hash_value]          CHAR(64)            NOT NULL,   -- System metadata: hash value used to detect changes in source attributes.</t>
-  </si>
-  <si>
-    <t>    [sys_data_source]         NVARCHAR(25)        NOT NULL,   -- System metadata: name of the source system.</t>
-  </si>
-  <si>
-    <t>=LEFT(A1,FIND(" ",A1)-1)</t>
-  </si>
-  <si>
-    <t>=MID(A1,FIND("-- ",A1)+3,LEN(A1))</t>
-  </si>
-  <si>
-    <t>[territory_key]             INT IDENTITY (1, 1) NOT NULL,   -- Surrogate key generated by the data warehouse.</t>
-  </si>
-  <si>
     <t>territory_name_bk</t>
   </si>
   <si>
@@ -1578,9 +1497,6 @@
     <t>AdventureWorks2024</t>
   </si>
   <si>
-    <t>Each row per product sold.</t>
-  </si>
-  <si>
     <t>Concatenate first name &amp; last name of source system.</t>
   </si>
   <si>
@@ -1599,9 +1515,6 @@
     <t>SalesOrderDetailID</t>
   </si>
   <si>
-    <t>sales_order_id_bk</t>
-  </si>
-  <si>
     <t>SalesOrderID</t>
   </si>
   <si>
@@ -1681,6 +1594,12 @@
   </si>
   <si>
     <t>Bring with lookup</t>
+  </si>
+  <si>
+    <t>sales_order_id</t>
+  </si>
+  <si>
+    <t>One row per sales order line item</t>
   </si>
 </sst>
 </file>
@@ -4601,10 +4520,10 @@
         <v>387</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="O8" s="108" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="P8" s="44"/>
       <c r="Q8" s="44"/>
@@ -4653,7 +4572,7 @@
         <v>50</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="J9" s="53" t="s">
         <v>5</v>
@@ -4759,10 +4678,10 @@
         <v>387</v>
       </c>
       <c r="N11" s="68" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="O11" s="69" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="P11" s="67"/>
       <c r="Q11" s="67"/>
@@ -5125,7 +5044,7 @@
         <v>438</v>
       </c>
       <c r="J2" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5157,7 +5076,7 @@
         <v>438</v>
       </c>
       <c r="J3" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5189,7 +5108,7 @@
         <v>438</v>
       </c>
       <c r="J4" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5221,7 +5140,7 @@
         <v>438</v>
       </c>
       <c r="J5" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -5253,7 +5172,7 @@
         <v>438</v>
       </c>
       <c r="J6" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -5285,7 +5204,7 @@
         <v>438</v>
       </c>
       <c r="J7" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -5317,7 +5236,7 @@
         <v>438</v>
       </c>
       <c r="J8" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -5349,7 +5268,7 @@
         <v>438</v>
       </c>
       <c r="J9" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -5381,7 +5300,7 @@
         <v>438</v>
       </c>
       <c r="J10" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -5413,7 +5332,7 @@
         <v>438</v>
       </c>
       <c r="J11" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -5445,7 +5364,7 @@
         <v>438</v>
       </c>
       <c r="J12" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -5477,7 +5396,7 @@
         <v>438</v>
       </c>
       <c r="J13" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -5509,7 +5428,7 @@
         <v>438</v>
       </c>
       <c r="J14" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -5541,7 +5460,7 @@
         <v>438</v>
       </c>
       <c r="J15" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -5573,7 +5492,7 @@
         <v>438</v>
       </c>
       <c r="J16" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -5605,7 +5524,7 @@
         <v>438</v>
       </c>
       <c r="J17" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -5637,7 +5556,7 @@
         <v>438</v>
       </c>
       <c r="J18" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5669,7 +5588,7 @@
         <v>438</v>
       </c>
       <c r="J19" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -5701,7 +5620,7 @@
         <v>438</v>
       </c>
       <c r="J20" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -5733,7 +5652,7 @@
         <v>438</v>
       </c>
       <c r="J21" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -5765,7 +5684,7 @@
         <v>438</v>
       </c>
       <c r="J22" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5797,7 +5716,7 @@
         <v>438</v>
       </c>
       <c r="J23" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5829,7 +5748,7 @@
         <v>438</v>
       </c>
       <c r="J24" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -5861,7 +5780,7 @@
         <v>438</v>
       </c>
       <c r="J25" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -5893,7 +5812,7 @@
         <v>438</v>
       </c>
       <c r="J26" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -5925,7 +5844,7 @@
         <v>438</v>
       </c>
       <c r="J27" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -5957,7 +5876,7 @@
         <v>438</v>
       </c>
       <c r="J28" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5989,7 +5908,7 @@
         <v>438</v>
       </c>
       <c r="J29" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6021,7 +5940,7 @@
         <v>438</v>
       </c>
       <c r="J30" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -6053,7 +5972,7 @@
         <v>438</v>
       </c>
       <c r="J31" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -6085,7 +6004,7 @@
         <v>438</v>
       </c>
       <c r="J32" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6117,7 +6036,7 @@
         <v>438</v>
       </c>
       <c r="J33" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -6149,7 +6068,7 @@
         <v>438</v>
       </c>
       <c r="J34" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -6181,7 +6100,7 @@
         <v>438</v>
       </c>
       <c r="J35" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6213,7 +6132,7 @@
         <v>438</v>
       </c>
       <c r="J36" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -6245,7 +6164,7 @@
         <v>438</v>
       </c>
       <c r="J37" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -6277,7 +6196,7 @@
         <v>438</v>
       </c>
       <c r="J38" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -6309,7 +6228,7 @@
         <v>438</v>
       </c>
       <c r="J39" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -6341,7 +6260,7 @@
         <v>438</v>
       </c>
       <c r="J40" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -6373,7 +6292,7 @@
         <v>438</v>
       </c>
       <c r="J41" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6405,7 +6324,7 @@
         <v>438</v>
       </c>
       <c r="J42" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -6437,7 +6356,7 @@
         <v>438</v>
       </c>
       <c r="J43" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -6469,7 +6388,7 @@
         <v>438</v>
       </c>
       <c r="J44" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -6501,7 +6420,7 @@
         <v>438</v>
       </c>
       <c r="J45" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -6533,7 +6452,7 @@
         <v>438</v>
       </c>
       <c r="J46" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -6565,7 +6484,7 @@
         <v>438</v>
       </c>
       <c r="J47" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -6597,7 +6516,7 @@
         <v>438</v>
       </c>
       <c r="J48" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7919,7 +7838,7 @@
         <v>387</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="E97" t="s">
         <v>432</v>
@@ -8006,10 +7925,10 @@
         <v>387</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="E100" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="F100" t="s">
         <v>392</v>
@@ -8018,7 +7937,7 @@
         <v>400</v>
       </c>
       <c r="H100" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="I100" t="s">
         <v>429</v>
@@ -8209,10 +8128,10 @@
         <v>80</v>
       </c>
       <c r="C107" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D107" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="E107" t="s">
         <v>288</v>
@@ -8238,10 +8157,10 @@
         <v>80</v>
       </c>
       <c r="C108" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D108" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="E108" t="s">
         <v>428</v>
@@ -8267,13 +8186,13 @@
         <v>80</v>
       </c>
       <c r="C109" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D109" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="E109" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="F109" t="s">
         <v>392</v>
@@ -8285,7 +8204,7 @@
         <v>401</v>
       </c>
       <c r="I109" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -8296,13 +8215,13 @@
         <v>80</v>
       </c>
       <c r="C110" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D110" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="E110" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="F110" t="s">
         <v>392</v>
@@ -8314,7 +8233,7 @@
         <v>401</v>
       </c>
       <c r="I110" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -8325,13 +8244,13 @@
         <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D111" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="E111" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="F111" t="s">
         <v>392</v>
@@ -8343,7 +8262,7 @@
         <v>401</v>
       </c>
       <c r="I111" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8354,13 +8273,13 @@
         <v>80</v>
       </c>
       <c r="C112" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D112" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="E112" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="F112" t="s">
         <v>392</v>
@@ -8372,7 +8291,7 @@
         <v>401</v>
       </c>
       <c r="I112" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -8383,13 +8302,13 @@
         <v>80</v>
       </c>
       <c r="C113" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D113" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="E113" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="F113" t="s">
         <v>392</v>
@@ -8401,7 +8320,7 @@
         <v>401</v>
       </c>
       <c r="I113" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8412,7 +8331,7 @@
         <v>80</v>
       </c>
       <c r="C114" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D114" t="s">
         <v>327</v>
@@ -8441,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="C115" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D115" t="s">
         <v>329</v>
@@ -8470,7 +8389,7 @@
         <v>80</v>
       </c>
       <c r="C116" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D116" t="s">
         <v>331</v>
@@ -8499,7 +8418,7 @@
         <v>80</v>
       </c>
       <c r="C117" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D117" t="s">
         <v>333</v>
@@ -8528,7 +8447,7 @@
         <v>80</v>
       </c>
       <c r="C118" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D118" t="s">
         <v>335</v>
@@ -8557,7 +8476,7 @@
         <v>80</v>
       </c>
       <c r="C119" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="D119" t="s">
         <v>337</v>
@@ -8589,10 +8508,10 @@
         <v>80</v>
       </c>
       <c r="C120" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D120" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="E120" t="s">
         <v>288</v>
@@ -8609,10 +8528,10 @@
         <v>80</v>
       </c>
       <c r="C121" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D121" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="F121" t="s">
         <v>392</v>
@@ -8626,13 +8545,13 @@
         <v>80</v>
       </c>
       <c r="C122" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D122" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="E122" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="F122" t="s">
         <v>392</v>
@@ -8646,10 +8565,10 @@
         <v>80</v>
       </c>
       <c r="C123" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D123" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="F123" t="s">
         <v>392</v>
@@ -8663,10 +8582,10 @@
         <v>80</v>
       </c>
       <c r="C124" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D124" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="F124" t="s">
         <v>392</v>
@@ -8680,10 +8599,10 @@
         <v>80</v>
       </c>
       <c r="C125" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D125" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="F125" t="s">
         <v>392</v>
@@ -8697,7 +8616,7 @@
         <v>80</v>
       </c>
       <c r="C126" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D126" t="s">
         <v>327</v>
@@ -8726,7 +8645,7 @@
         <v>80</v>
       </c>
       <c r="C127" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D127" t="s">
         <v>329</v>
@@ -8755,7 +8674,7 @@
         <v>80</v>
       </c>
       <c r="C128" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D128" t="s">
         <v>331</v>
@@ -8784,7 +8703,7 @@
         <v>80</v>
       </c>
       <c r="C129" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D129" t="s">
         <v>333</v>
@@ -8813,7 +8732,7 @@
         <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D130" t="s">
         <v>335</v>
@@ -8842,7 +8761,7 @@
         <v>80</v>
       </c>
       <c r="C131" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D131" t="s">
         <v>337</v>
@@ -8871,13 +8790,13 @@
         <v>82</v>
       </c>
       <c r="C132" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D132" t="s">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="E132" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="F132" t="s">
         <v>392</v>
@@ -8886,10 +8805,10 @@
         <v>393</v>
       </c>
       <c r="H132" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I132" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="J132" t="s">
         <v>423</v>
@@ -8903,13 +8822,13 @@
         <v>82</v>
       </c>
       <c r="C133" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D133" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E133" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="F133" t="s">
         <v>392</v>
@@ -8918,10 +8837,10 @@
         <v>393</v>
       </c>
       <c r="H133" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I133" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="J133" t="s">
         <v>423</v>
@@ -8935,13 +8854,13 @@
         <v>82</v>
       </c>
       <c r="C134" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D134" t="s">
         <v>240</v>
       </c>
       <c r="E134" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="F134" t="s">
         <v>392</v>
@@ -8950,13 +8869,13 @@
         <v>393</v>
       </c>
       <c r="H134" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="I134" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="J134" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8967,13 +8886,13 @@
         <v>82</v>
       </c>
       <c r="C135" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D135" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="E135" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="F135" t="s">
         <v>392</v>
@@ -8982,10 +8901,10 @@
         <v>393</v>
       </c>
       <c r="H135" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="I135" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8996,13 +8915,13 @@
         <v>82</v>
       </c>
       <c r="C136" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D136" t="s">
         <v>388</v>
       </c>
       <c r="E136" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="F136" t="s">
         <v>392</v>
@@ -9011,13 +8930,13 @@
         <v>393</v>
       </c>
       <c r="H136" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="I136" t="s">
         <v>403</v>
       </c>
       <c r="J136" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -9028,13 +8947,13 @@
         <v>82</v>
       </c>
       <c r="C137" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D137" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="E137" t="s">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="F137" t="s">
         <v>392</v>
@@ -9043,13 +8962,13 @@
         <v>393</v>
       </c>
       <c r="H137" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="I137" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="J137" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -9060,13 +8979,13 @@
         <v>82</v>
       </c>
       <c r="C138" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D138" t="s">
         <v>442</v>
       </c>
       <c r="E138" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="F138" t="s">
         <v>392</v>
@@ -9075,13 +8994,13 @@
         <v>393</v>
       </c>
       <c r="H138" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="I138" t="s">
         <v>406</v>
       </c>
       <c r="J138" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -9092,28 +9011,28 @@
         <v>82</v>
       </c>
       <c r="C139" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D139" t="s">
         <v>287</v>
       </c>
       <c r="E139" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="F139" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="G139" t="s">
         <v>393</v>
       </c>
       <c r="H139" t="s">
+        <v>475</v>
+      </c>
+      <c r="I139" t="s">
+        <v>488</v>
+      </c>
+      <c r="J139" t="s">
         <v>503</v>
-      </c>
-      <c r="I139" t="s">
-        <v>517</v>
-      </c>
-      <c r="J139" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -9124,13 +9043,13 @@
         <v>82</v>
       </c>
       <c r="C140" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D140" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="E140" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="F140" t="s">
         <v>392</v>
@@ -9139,10 +9058,10 @@
         <v>393</v>
       </c>
       <c r="H140" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I140" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -9153,13 +9072,13 @@
         <v>82</v>
       </c>
       <c r="C141" t="s">
+        <v>469</v>
+      </c>
+      <c r="D141" t="s">
+        <v>500</v>
+      </c>
+      <c r="E141" t="s">
         <v>496</v>
-      </c>
-      <c r="D141" t="s">
-        <v>529</v>
-      </c>
-      <c r="E141" t="s">
-        <v>525</v>
       </c>
       <c r="F141" t="s">
         <v>392</v>
@@ -9168,10 +9087,10 @@
         <v>393</v>
       </c>
       <c r="H141" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I141" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -9182,13 +9101,13 @@
         <v>82</v>
       </c>
       <c r="C142" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D142" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="E142" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="F142" t="s">
         <v>392</v>
@@ -9197,10 +9116,10 @@
         <v>393</v>
       </c>
       <c r="H142" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I142" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -9211,13 +9130,13 @@
         <v>82</v>
       </c>
       <c r="C143" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D143" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="E143" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="F143" t="s">
         <v>392</v>
@@ -9226,10 +9145,10 @@
         <v>393</v>
       </c>
       <c r="H143" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I143" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -9240,7 +9159,7 @@
         <v>82</v>
       </c>
       <c r="C144" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D144" t="s">
         <v>327</v>
@@ -9269,7 +9188,7 @@
         <v>82</v>
       </c>
       <c r="C145" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D145" t="s">
         <v>329</v>
@@ -9298,7 +9217,7 @@
         <v>82</v>
       </c>
       <c r="C146" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D146" t="s">
         <v>331</v>
@@ -9327,7 +9246,7 @@
         <v>82</v>
       </c>
       <c r="C147" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D147" t="s">
         <v>333</v>
@@ -9356,7 +9275,7 @@
         <v>82</v>
       </c>
       <c r="C148" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D148" t="s">
         <v>335</v>
@@ -9385,7 +9304,7 @@
         <v>82</v>
       </c>
       <c r="C149" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D149" t="s">
         <v>337</v>
@@ -9660,21 +9579,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
-        <v>468</v>
-      </c>
+      <c r="A1" s="91"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
-        <v>469</v>
-      </c>
-      <c r="E2" s="92" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G2,FIND("]",G2)),"]",""),"[",""),"    ","")</f>
-        <v>territory_key</v>
-      </c>
-      <c r="G2" s="83" t="s">
-        <v>470</v>
-      </c>
+      <c r="A2" s="91"/>
+      <c r="E2" s="92"/>
       <c r="M2" s="87"/>
       <c r="N2" s="88"/>
       <c r="Q2" s="87"/>
@@ -9684,22 +9593,7 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="84"/>
-      <c r="B3" s="83">
-        <v>1</v>
-      </c>
-      <c r="C3" s="83" t="s">
-        <v>406</v>
-      </c>
-      <c r="D3" s="83" t="s">
-        <v>444</v>
-      </c>
-      <c r="E3" s="92" t="str">
-        <f t="shared" ref="E3:E6" si="0">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LEFT(G3,FIND("]",G3)),"]",""),"[",""),"    ","")</f>
-        <v>territory_name_bk</v>
-      </c>
-      <c r="G3" s="83" t="s">
-        <v>459</v>
-      </c>
+      <c r="E3" s="92"/>
       <c r="Q3" s="87"/>
       <c r="R3" s="88"/>
       <c r="S3" s="87"/>
@@ -9709,22 +9603,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="84"/>
-      <c r="B4" s="83">
-        <v>2</v>
-      </c>
-      <c r="C4" s="83" t="s">
-        <v>429</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>432</v>
-      </c>
-      <c r="E4" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>territory_group</v>
-      </c>
-      <c r="G4" s="83" t="s">
-        <v>460</v>
-      </c>
+      <c r="E4" s="92"/>
       <c r="Q4" s="87"/>
       <c r="R4" s="88"/>
       <c r="S4" s="87"/>
@@ -9734,22 +9613,9 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="84"/>
-      <c r="B5" s="84">
-        <v>3</v>
-      </c>
-      <c r="C5" s="84" t="s">
-        <v>430</v>
-      </c>
-      <c r="D5" s="83" t="s">
-        <v>433</v>
-      </c>
-      <c r="E5" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>country_region_code</v>
-      </c>
-      <c r="G5" s="83" t="s">
-        <v>461</v>
-      </c>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="E5" s="92"/>
       <c r="Q5" s="87"/>
       <c r="R5" s="88"/>
       <c r="S5" s="87"/>
@@ -9759,159 +9625,49 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="84"/>
-      <c r="B6" s="83">
-        <v>4</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>431</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>434</v>
-      </c>
-      <c r="E6" s="92" t="str">
-        <f t="shared" si="0"/>
-        <v>country_name</v>
-      </c>
-      <c r="G6" s="83" t="s">
-        <v>462</v>
-      </c>
+      <c r="E6" s="92"/>
       <c r="Q6" s="87"/>
       <c r="R6" s="88"/>
       <c r="Y6" s="87"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="84"/>
-      <c r="B7" s="83">
-        <v>5</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>445</v>
-      </c>
-      <c r="D7" s="83" t="s">
-        <v>446</v>
-      </c>
-      <c r="G7" s="83" t="s">
-        <v>457</v>
-      </c>
       <c r="Q7" s="87"/>
       <c r="R7" s="88"/>
       <c r="Y7" s="87"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="84"/>
-      <c r="B8" s="83">
-        <v>6</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>447</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>448</v>
-      </c>
-      <c r="E8" s="83" t="str">
-        <f t="shared" ref="E8:E12" si="1">LEFT(G8, FIND("]", G8))</f>
-        <v>    [sys_insert_date]</v>
-      </c>
-      <c r="G8" s="83" t="s">
-        <v>463</v>
-      </c>
       <c r="Q8" s="87"/>
       <c r="R8" s="88"/>
       <c r="Y8" s="87"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="84"/>
-      <c r="B9" s="83">
-        <v>7</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>449</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>450</v>
-      </c>
-      <c r="E9" s="83" t="str">
-        <f t="shared" si="1"/>
-        <v>    [sys_update_date]</v>
-      </c>
-      <c r="G9" s="83" t="s">
-        <v>464</v>
-      </c>
       <c r="N9" s="87"/>
       <c r="O9" s="88"/>
       <c r="V9" s="87"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="84"/>
-      <c r="B10" s="83">
-        <v>8</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>451</v>
-      </c>
-      <c r="D10" s="83" t="s">
-        <v>452</v>
-      </c>
-      <c r="E10" s="83" t="str">
-        <f t="shared" si="1"/>
-        <v>    [sys_delete_date]</v>
-      </c>
-      <c r="G10" s="83" t="s">
-        <v>465</v>
-      </c>
       <c r="N10" s="87"/>
       <c r="O10" s="88"/>
       <c r="V10" s="87"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="84"/>
-      <c r="B11" s="83">
-        <v>9</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>453</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>454</v>
-      </c>
-      <c r="E11" s="83" t="str">
-        <f t="shared" si="1"/>
-        <v>    [sys_hash_value]</v>
-      </c>
-      <c r="G11" s="83" t="s">
-        <v>466</v>
-      </c>
       <c r="N11" s="87"/>
       <c r="O11" s="88"/>
       <c r="V11" s="87"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="84"/>
-      <c r="B12" s="83">
-        <v>10</v>
-      </c>
-      <c r="C12" s="83" t="s">
-        <v>455</v>
-      </c>
-      <c r="D12" s="83" t="s">
-        <v>456</v>
-      </c>
-      <c r="E12" s="83" t="str">
-        <f t="shared" si="1"/>
-        <v>    [sys_data_source]</v>
-      </c>
-      <c r="G12" s="83" t="s">
-        <v>467</v>
-      </c>
       <c r="N12" s="87"/>
       <c r="O12" s="88"/>
       <c r="V12" s="87"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="84"/>
-      <c r="G13" s="83" t="s">
-        <v>458</v>
-      </c>
       <c r="N13" s="87"/>
       <c r="O13" s="88"/>
       <c r="V13" s="87"/>
